--- a/plantillas/horario_mes_anterior_EJEMPLO.xlsx
+++ b/plantillas/horario_mes_anterior_EJEMPLO.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'PLANIFICACION_MENSUAL'!$A$1:$V$433</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'RESUMEN_EJECUTIVOS'!$A$1:$N$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'MATRIZ_COBERTURA'!$A$1:$P$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ALERTAS'!$A$1:$E$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ALERTAS'!$A$1:$E$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -742,13 +742,13 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="S2" s="5" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="T2" s="5" t="n">
+        <v>0.6354166666666666</v>
+      </c>
+      <c r="U2" s="5" t="n">
         <v>0.6770833333333334</v>
-      </c>
-      <c r="U2" s="5" t="n">
-        <v>0.71875</v>
       </c>
       <c r="V2" s="3">
         <f>IF(COUNT(T2:U2)=2,ROUND((U2-T2)*1440,0),0)</f>
@@ -830,13 +830,13 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="S3" s="5" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="T3" s="5" t="n">
+        <v>0.6354166666666666</v>
+      </c>
+      <c r="U3" s="5" t="n">
         <v>0.6770833333333334</v>
-      </c>
-      <c r="U3" s="5" t="n">
-        <v>0.71875</v>
       </c>
       <c r="V3" s="3">
         <f>IF(COUNT(T3:U3)=2,ROUND((U3-T3)*1440,0),0)</f>
@@ -1175,16 +1175,16 @@
         <v/>
       </c>
       <c r="R7" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="U7" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="V7" s="3">
         <f>IF(COUNT(T7:U7)=2,ROUND((U7-T7)*1440,0),0)</f>
@@ -1266,13 +1266,13 @@
         <v>0.4270833333333333</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="U8" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="V8" s="3">
         <f>IF(COUNT(T8:U8)=2,ROUND((U8-T8)*1440,0),0)</f>
@@ -1351,16 +1351,16 @@
         <v/>
       </c>
       <c r="R9" s="5" t="n">
-        <v>0.4270833333333333</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>0.53125</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="U9" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="V9" s="3">
         <f>IF(COUNT(T9:U9)=2,ROUND((U9-T9)*1440,0),0)</f>
@@ -1679,16 +1679,16 @@
         <v/>
       </c>
       <c r="R13" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="U13" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="V13" s="3">
         <f>IF(COUNT(T13:U13)=2,ROUND((U13-T13)*1440,0),0)</f>
@@ -1770,13 +1770,13 @@
         <v>0.4270833333333333</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="U14" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="V14" s="3">
         <f>IF(COUNT(T14:U14)=2,ROUND((U14-T14)*1440,0),0)</f>
@@ -1855,16 +1855,16 @@
         <v/>
       </c>
       <c r="R15" s="5" t="n">
-        <v>0.4270833333333333</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>0.53125</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="U15" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="V15" s="3">
         <f>IF(COUNT(T15:U15)=2,ROUND((U15-T15)*1440,0),0)</f>
@@ -2022,13 +2022,13 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="U17" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="V17" s="3">
         <f>IF(COUNT(T17:U17)=2,ROUND((U17-T17)*1440,0),0)</f>
@@ -2110,13 +2110,13 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="U18" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="V18" s="3">
         <f>IF(COUNT(T18:U18)=2,ROUND((U18-T18)*1440,0),0)</f>
@@ -2195,16 +2195,16 @@
         <v/>
       </c>
       <c r="R19" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.65625</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.53125</v>
       </c>
       <c r="U19" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5729166666666666</v>
       </c>
       <c r="V19" s="3">
         <f>IF(COUNT(T19:U19)=2,ROUND((U19-T19)*1440,0),0)</f>
@@ -2286,13 +2286,13 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="T20" s="5" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="U20" s="5" t="n">
         <v>0.5104166666666666</v>
-      </c>
-      <c r="U20" s="5" t="n">
-        <v>0.5520833333333334</v>
       </c>
       <c r="V20" s="3">
         <f>IF(COUNT(T20:U20)=2,ROUND((U20-T20)*1440,0),0)</f>
@@ -2374,13 +2374,13 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="T21" s="5" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="U21" s="5" t="n">
         <v>0.5104166666666666</v>
-      </c>
-      <c r="U21" s="5" t="n">
-        <v>0.5520833333333334</v>
       </c>
       <c r="V21" s="3">
         <f>IF(COUNT(T21:U21)=2,ROUND((U21-T21)*1440,0),0)</f>
@@ -2543,16 +2543,16 @@
         <v/>
       </c>
       <c r="R23" s="5" t="n">
-        <v>0.5</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.71875</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.5625</v>
       </c>
       <c r="U23" s="5" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="V23" s="3">
         <f>IF(COUNT(T23:U23)=2,ROUND((U23-T23)*1440,0),0)</f>
@@ -2631,16 +2631,16 @@
         <v/>
       </c>
       <c r="R24" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.71875</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
       <c r="U24" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="V24" s="3">
         <f>IF(COUNT(T24:U24)=2,ROUND((U24-T24)*1440,0),0)</f>
@@ -2719,16 +2719,16 @@
         <v/>
       </c>
       <c r="R25" s="5" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S25" s="5" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.71875</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.59375</v>
       </c>
       <c r="U25" s="5" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="V25" s="3">
         <f>IF(COUNT(T25:U25)=2,ROUND((U25-T25)*1440,0),0)</f>
@@ -2807,16 +2807,16 @@
         <v/>
       </c>
       <c r="R26" s="5" t="n">
-        <v>0.5</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S26" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="U26" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="V26" s="3">
         <f>IF(COUNT(T26:U26)=2,ROUND((U26-T26)*1440,0),0)</f>
@@ -2895,7 +2895,7 @@
         <v/>
       </c>
       <c r="R27" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S27" s="5" t="n">
         <v>0.71875</v>
@@ -3059,7 +3059,7 @@
         <v/>
       </c>
       <c r="R29" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.53125</v>
       </c>
       <c r="S29" s="5" t="n">
         <v>0.7708333333333334</v>
@@ -3147,16 +3147,16 @@
         <v/>
       </c>
       <c r="R30" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="S30" s="5" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.78125</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.65625</v>
       </c>
       <c r="U30" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="V30" s="3">
         <f>IF(COUNT(T30:U30)=2,ROUND((U30-T30)*1440,0),0)</f>
@@ -3314,13 +3314,13 @@
         <v>0.4270833333333333</v>
       </c>
       <c r="S32" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="T32" s="5" t="n">
+        <v>0.5104166666666666</v>
+      </c>
+      <c r="U32" s="5" t="n">
         <v>0.5520833333333334</v>
-      </c>
-      <c r="U32" s="5" t="n">
-        <v>0.59375</v>
       </c>
       <c r="V32" s="3">
         <f>IF(COUNT(T32:U32)=2,ROUND((U32-T32)*1440,0),0)</f>
@@ -3402,13 +3402,13 @@
         <v>0.4270833333333333</v>
       </c>
       <c r="S33" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="T33" s="5" t="n">
+        <v>0.5104166666666666</v>
+      </c>
+      <c r="U33" s="5" t="n">
         <v>0.5520833333333334</v>
-      </c>
-      <c r="U33" s="5" t="n">
-        <v>0.59375</v>
       </c>
       <c r="V33" s="3">
         <f>IF(COUNT(T33:U33)=2,ROUND((U33-T33)*1440,0),0)</f>
@@ -3487,10 +3487,10 @@
         <v/>
       </c>
       <c r="R34" s="5" t="n">
-        <v>0.4375</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="S34" s="5" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.6875</v>
       </c>
       <c r="T34" s="5" t="n">
         <v>0.5520833333333334</v>
@@ -3575,16 +3575,16 @@
         <v/>
       </c>
       <c r="R35" s="5" t="n">
-        <v>0.4375</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="S35" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="T35" s="5" t="n">
-        <v>0.53125</v>
+        <v>0.5625</v>
       </c>
       <c r="U35" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="V35" s="3">
         <f>IF(COUNT(T35:U35)=2,ROUND((U35-T35)*1440,0),0)</f>
@@ -3663,7 +3663,7 @@
         <v/>
       </c>
       <c r="R36" s="5" t="n">
-        <v>0.4375</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="S36" s="5" t="n">
         <v>0.6770833333333334</v>
@@ -3906,13 +3906,13 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="S39" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.59375</v>
       </c>
       <c r="T39" s="5" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="U39" s="5" t="n">
         <v>0.5104166666666666</v>
-      </c>
-      <c r="U39" s="5" t="n">
-        <v>0.5520833333333334</v>
       </c>
       <c r="V39" s="3">
         <f>IF(COUNT(T39:U39)=2,ROUND((U39-T39)*1440,0),0)</f>
@@ -3991,16 +3991,16 @@
         <v/>
       </c>
       <c r="R40" s="5" t="n">
-        <v>0.4270833333333333</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="S40" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="T40" s="5" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.46875</v>
       </c>
       <c r="U40" s="5" t="n">
-        <v>0.5625</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="V40" s="3">
         <f>IF(COUNT(T40:U40)=2,ROUND((U40-T40)*1440,0),0)</f>
@@ -4082,13 +4082,13 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="S41" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.625</v>
       </c>
       <c r="T41" s="5" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="U41" s="5" t="n">
         <v>0.5104166666666666</v>
-      </c>
-      <c r="U41" s="5" t="n">
-        <v>0.5520833333333334</v>
       </c>
       <c r="V41" s="3">
         <f>IF(COUNT(T41:U41)=2,ROUND((U41-T41)*1440,0),0)</f>
@@ -4170,13 +4170,13 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="S42" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="T42" s="5" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="U42" s="5" t="n">
         <v>0.5104166666666666</v>
-      </c>
-      <c r="U42" s="5" t="n">
-        <v>0.5520833333333334</v>
       </c>
       <c r="V42" s="3">
         <f>IF(COUNT(T42:U42)=2,ROUND((U42-T42)*1440,0),0)</f>
@@ -4345,10 +4345,10 @@
         <v>0.7395833333333334</v>
       </c>
       <c r="T44" s="5" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5729166666666666</v>
       </c>
       <c r="U44" s="5" t="n">
-        <v>0.625</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="V44" s="3">
         <f>IF(COUNT(T44:U44)=2,ROUND((U44-T44)*1440,0),0)</f>
@@ -4433,10 +4433,10 @@
         <v>0.7395833333333334</v>
       </c>
       <c r="T45" s="5" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5729166666666666</v>
       </c>
       <c r="U45" s="5" t="n">
-        <v>0.625</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="V45" s="3">
         <f>IF(COUNT(T45:U45)=2,ROUND((U45-T45)*1440,0),0)</f>
@@ -4515,7 +4515,7 @@
         <v/>
       </c>
       <c r="R46" s="5" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S46" s="5" t="n">
         <v>0.71875</v>
@@ -4603,16 +4603,16 @@
         <v/>
       </c>
       <c r="R47" s="5" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S47" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.6875</v>
       </c>
       <c r="T47" s="5" t="n">
+        <v>0.5520833333333334</v>
+      </c>
+      <c r="U47" s="5" t="n">
         <v>0.59375</v>
-      </c>
-      <c r="U47" s="5" t="n">
-        <v>0.6354166666666666</v>
       </c>
       <c r="V47" s="3">
         <f>IF(COUNT(T47:U47)=2,ROUND((U47-T47)*1440,0),0)</f>
@@ -4691,7 +4691,7 @@
         <v/>
       </c>
       <c r="R48" s="5" t="n">
-        <v>0.5</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S48" s="5" t="n">
         <v>0.71875</v>
@@ -4855,16 +4855,16 @@
         <v/>
       </c>
       <c r="R50" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="S50" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="T50" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="U50" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="V50" s="3">
         <f>IF(COUNT(T50:U50)=2,ROUND((U50-T50)*1440,0),0)</f>
@@ -4943,16 +4943,16 @@
         <v/>
       </c>
       <c r="R51" s="5" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.5</v>
       </c>
       <c r="S51" s="5" t="n">
-        <v>0.75</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="T51" s="5" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="U51" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="V51" s="3">
         <f>IF(COUNT(T51:U51)=2,ROUND((U51-T51)*1440,0),0)</f>
@@ -5119,7 +5119,7 @@
         <v/>
       </c>
       <c r="R53" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S53" s="5" t="n">
         <v>0.71875</v>
@@ -5207,16 +5207,16 @@
         <v/>
       </c>
       <c r="R54" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S54" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.65625</v>
       </c>
       <c r="T54" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="U54" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.5625</v>
       </c>
       <c r="V54" s="3">
         <f>IF(COUNT(T54:U54)=2,ROUND((U54-T54)*1440,0),0)</f>
@@ -5371,16 +5371,16 @@
         <v/>
       </c>
       <c r="R56" s="5" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="S56" s="5" t="n">
-        <v>0.78125</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="T56" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="U56" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.71875</v>
       </c>
       <c r="V56" s="3">
         <f>IF(COUNT(T56:U56)=2,ROUND((U56-T56)*1440,0),0)</f>
@@ -5459,16 +5459,16 @@
         <v/>
       </c>
       <c r="R57" s="5" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5729166666666666</v>
       </c>
       <c r="S57" s="5" t="n">
-        <v>0.78125</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="T57" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="U57" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.71875</v>
       </c>
       <c r="V57" s="3">
         <f>IF(COUNT(T57:U57)=2,ROUND((U57-T57)*1440,0),0)</f>
@@ -5626,13 +5626,13 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="S59" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.59375</v>
       </c>
       <c r="T59" s="5" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="U59" s="5" t="n">
         <v>0.5104166666666666</v>
-      </c>
-      <c r="U59" s="5" t="n">
-        <v>0.5520833333333334</v>
       </c>
       <c r="V59" s="3">
         <f>IF(COUNT(T59:U59)=2,ROUND((U59-T59)*1440,0),0)</f>
@@ -5714,13 +5714,13 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="S60" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.59375</v>
       </c>
       <c r="T60" s="5" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="U60" s="5" t="n">
         <v>0.5104166666666666</v>
-      </c>
-      <c r="U60" s="5" t="n">
-        <v>0.5520833333333334</v>
       </c>
       <c r="V60" s="3">
         <f>IF(COUNT(T60:U60)=2,ROUND((U60-T60)*1440,0),0)</f>
@@ -5802,13 +5802,13 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="S61" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.625</v>
       </c>
       <c r="T61" s="5" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="U61" s="5" t="n">
         <v>0.5104166666666666</v>
-      </c>
-      <c r="U61" s="5" t="n">
-        <v>0.5520833333333334</v>
       </c>
       <c r="V61" s="3">
         <f>IF(COUNT(T61:U61)=2,ROUND((U61-T61)*1440,0),0)</f>
@@ -5890,13 +5890,13 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="S62" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.625</v>
       </c>
       <c r="T62" s="5" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="U62" s="5" t="n">
         <v>0.5104166666666666</v>
-      </c>
-      <c r="U62" s="5" t="n">
-        <v>0.5520833333333334</v>
       </c>
       <c r="V62" s="3">
         <f>IF(COUNT(T62:U62)=2,ROUND((U62-T62)*1440,0),0)</f>
@@ -5978,13 +5978,13 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="S63" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="T63" s="5" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="U63" s="5" t="n">
         <v>0.5104166666666666</v>
-      </c>
-      <c r="U63" s="5" t="n">
-        <v>0.5520833333333334</v>
       </c>
       <c r="V63" s="3">
         <f>IF(COUNT(T63:U63)=2,ROUND((U63-T63)*1440,0),0)</f>
@@ -6226,13 +6226,13 @@
         <v>0.4583333333333333</v>
       </c>
       <c r="S66" s="5" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="T66" s="5" t="n">
+        <v>0.5520833333333334</v>
+      </c>
+      <c r="U66" s="5" t="n">
         <v>0.59375</v>
-      </c>
-      <c r="U66" s="5" t="n">
-        <v>0.6354166666666666</v>
       </c>
       <c r="V66" s="3">
         <f>IF(COUNT(T66:U66)=2,ROUND((U66-T66)*1440,0),0)</f>
@@ -6314,13 +6314,13 @@
         <v>0.4583333333333333</v>
       </c>
       <c r="S67" s="5" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.71875</v>
       </c>
       <c r="T67" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.59375</v>
       </c>
       <c r="U67" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="V67" s="3">
         <f>IF(COUNT(T67:U67)=2,ROUND((U67-T67)*1440,0),0)</f>
@@ -6399,16 +6399,16 @@
         <v/>
       </c>
       <c r="R68" s="5" t="n">
-        <v>0.5</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S68" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="T68" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="U68" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="V68" s="3">
         <f>IF(COUNT(T68:U68)=2,ROUND((U68-T68)*1440,0),0)</f>
@@ -6487,7 +6487,7 @@
         <v/>
       </c>
       <c r="R69" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S69" s="5" t="n">
         <v>0.71875</v>
@@ -6651,16 +6651,16 @@
         <v/>
       </c>
       <c r="R71" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="S71" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.75</v>
       </c>
       <c r="T71" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="U71" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.65625</v>
       </c>
       <c r="V71" s="3">
         <f>IF(COUNT(T71:U71)=2,ROUND((U71-T71)*1440,0),0)</f>
@@ -6739,16 +6739,16 @@
         <v/>
       </c>
       <c r="R72" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="S72" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.75</v>
       </c>
       <c r="T72" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="U72" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.65625</v>
       </c>
       <c r="V72" s="3">
         <f>IF(COUNT(T72:U72)=2,ROUND((U72-T72)*1440,0),0)</f>
@@ -6827,16 +6827,16 @@
         <v/>
       </c>
       <c r="R73" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S73" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="T73" s="5" t="n">
+        <v>0.5520833333333334</v>
+      </c>
+      <c r="U73" s="5" t="n">
         <v>0.59375</v>
-      </c>
-      <c r="U73" s="5" t="n">
-        <v>0.6354166666666666</v>
       </c>
       <c r="V73" s="3">
         <f>IF(COUNT(T73:U73)=2,ROUND((U73-T73)*1440,0),0)</f>
@@ -6915,7 +6915,7 @@
         <v/>
       </c>
       <c r="R74" s="5" t="n">
-        <v>0.5</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S74" s="5" t="n">
         <v>0.71875</v>
@@ -7003,16 +7003,16 @@
         <v/>
       </c>
       <c r="R75" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S75" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.65625</v>
       </c>
       <c r="T75" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.53125</v>
       </c>
       <c r="U75" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.5729166666666666</v>
       </c>
       <c r="V75" s="3">
         <f>IF(COUNT(T75:U75)=2,ROUND((U75-T75)*1440,0),0)</f>
@@ -7170,13 +7170,13 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="S77" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.59375</v>
       </c>
       <c r="T77" s="5" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="U77" s="5" t="n">
         <v>0.5104166666666666</v>
-      </c>
-      <c r="U77" s="5" t="n">
-        <v>0.5520833333333334</v>
       </c>
       <c r="V77" s="3">
         <f>IF(COUNT(T77:U77)=2,ROUND((U77-T77)*1440,0),0)</f>
@@ -7258,13 +7258,13 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="S78" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.59375</v>
       </c>
       <c r="T78" s="5" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="U78" s="5" t="n">
         <v>0.5104166666666666</v>
-      </c>
-      <c r="U78" s="5" t="n">
-        <v>0.5520833333333334</v>
       </c>
       <c r="V78" s="3">
         <f>IF(COUNT(T78:U78)=2,ROUND((U78-T78)*1440,0),0)</f>
@@ -7343,16 +7343,16 @@
         <v/>
       </c>
       <c r="R79" s="5" t="n">
-        <v>0.4270833333333333</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="S79" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="T79" s="5" t="n">
-        <v>0.53125</v>
+        <v>0.46875</v>
       </c>
       <c r="U79" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="V79" s="3">
         <f>IF(COUNT(T79:U79)=2,ROUND((U79-T79)*1440,0),0)</f>
@@ -7434,13 +7434,13 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="S80" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.625</v>
       </c>
       <c r="T80" s="5" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="U80" s="5" t="n">
         <v>0.5104166666666666</v>
-      </c>
-      <c r="U80" s="5" t="n">
-        <v>0.5520833333333334</v>
       </c>
       <c r="V80" s="3">
         <f>IF(COUNT(T80:U80)=2,ROUND((U80-T80)*1440,0),0)</f>
@@ -7525,10 +7525,10 @@
         <v>0.6354166666666666</v>
       </c>
       <c r="T81" s="5" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="U81" s="5" t="n">
         <v>0.5104166666666666</v>
-      </c>
-      <c r="U81" s="5" t="n">
-        <v>0.5520833333333334</v>
       </c>
       <c r="V81" s="3">
         <f>IF(COUNT(T81:U81)=2,ROUND((U81-T81)*1440,0),0)</f>
@@ -7686,13 +7686,13 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="S83" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="T83" s="5" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="U83" s="5" t="n">
         <v>0.5104166666666666</v>
-      </c>
-      <c r="U83" s="5" t="n">
-        <v>0.5520833333333334</v>
       </c>
       <c r="V83" s="3">
         <f>IF(COUNT(T83:U83)=2,ROUND((U83-T83)*1440,0),0)</f>
@@ -7774,13 +7774,13 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="S84" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="T84" s="5" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="U84" s="5" t="n">
         <v>0.5104166666666666</v>
-      </c>
-      <c r="U84" s="5" t="n">
-        <v>0.5520833333333334</v>
       </c>
       <c r="V84" s="3">
         <f>IF(COUNT(T84:U84)=2,ROUND((U84-T84)*1440,0),0)</f>
@@ -7943,16 +7943,16 @@
         <v/>
       </c>
       <c r="R86" s="5" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="S86" s="5" t="n">
-        <v>0.78125</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="T86" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="U86" s="5" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.71875</v>
       </c>
       <c r="V86" s="3">
         <f>IF(COUNT(T86:U86)=2,ROUND((U86-T86)*1440,0),0)</f>
@@ -8031,16 +8031,16 @@
         <v/>
       </c>
       <c r="R87" s="5" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="S87" s="5" t="n">
-        <v>0.78125</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="T87" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="U87" s="5" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.71875</v>
       </c>
       <c r="V87" s="3">
         <f>IF(COUNT(T87:U87)=2,ROUND((U87-T87)*1440,0),0)</f>
@@ -8119,16 +8119,16 @@
         <v/>
       </c>
       <c r="R88" s="5" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="S88" s="5" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="T88" s="5" t="n">
+        <v>0.6354166666666666</v>
+      </c>
+      <c r="U88" s="5" t="n">
         <v>0.6770833333333334</v>
-      </c>
-      <c r="U88" s="5" t="n">
-        <v>0.71875</v>
       </c>
       <c r="V88" s="3">
         <f>IF(COUNT(T88:U88)=2,ROUND((U88-T88)*1440,0),0)</f>
@@ -8207,16 +8207,16 @@
         <v/>
       </c>
       <c r="R89" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.53125</v>
       </c>
       <c r="S89" s="5" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.78125</v>
       </c>
       <c r="T89" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.65625</v>
       </c>
       <c r="U89" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="V89" s="3">
         <f>IF(COUNT(T89:U89)=2,ROUND((U89-T89)*1440,0),0)</f>
@@ -8298,13 +8298,13 @@
         <v>0.5416666666666666</v>
       </c>
       <c r="S90" s="5" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="T90" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="U90" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.71875</v>
       </c>
       <c r="V90" s="3">
         <f>IF(COUNT(T90:U90)=2,ROUND((U90-T90)*1440,0),0)</f>
@@ -8535,16 +8535,16 @@
         <v/>
       </c>
       <c r="R93" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.5</v>
       </c>
       <c r="S93" s="5" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="T93" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="U93" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="V93" s="3">
         <f>IF(COUNT(T93:U93)=2,ROUND((U93-T93)*1440,0),0)</f>
@@ -8623,16 +8623,16 @@
         <v/>
       </c>
       <c r="R94" s="5" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S94" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="T94" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="U94" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="V94" s="3">
         <f>IF(COUNT(T94:U94)=2,ROUND((U94-T94)*1440,0),0)</f>
@@ -8711,7 +8711,7 @@
         <v/>
       </c>
       <c r="R95" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S95" s="5" t="n">
         <v>0.71875</v>
@@ -8799,16 +8799,16 @@
         <v/>
       </c>
       <c r="R96" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S96" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="T96" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="U96" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="V96" s="3">
         <f>IF(COUNT(T96:U96)=2,ROUND((U96-T96)*1440,0),0)</f>
@@ -8963,16 +8963,16 @@
         <v/>
       </c>
       <c r="R98" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="S98" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="T98" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="U98" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="V98" s="3">
         <f>IF(COUNT(T98:U98)=2,ROUND((U98-T98)*1440,0),0)</f>
@@ -9051,16 +9051,16 @@
         <v/>
       </c>
       <c r="R99" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="S99" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="T99" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="U99" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="V99" s="3">
         <f>IF(COUNT(T99:U99)=2,ROUND((U99-T99)*1440,0),0)</f>
@@ -9139,16 +9139,16 @@
         <v/>
       </c>
       <c r="R100" s="5" t="n">
-        <v>0.4375</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="S100" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="T100" s="5" t="n">
-        <v>0.53125</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="U100" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="V100" s="3">
         <f>IF(COUNT(T100:U100)=2,ROUND((U100-T100)*1440,0),0)</f>
@@ -9227,16 +9227,16 @@
         <v/>
       </c>
       <c r="R101" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="S101" s="5" t="n">
         <v>0.6354166666666666</v>
       </c>
       <c r="T101" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.5</v>
       </c>
       <c r="U101" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="V101" s="3">
         <f>IF(COUNT(T101:U101)=2,ROUND((U101-T101)*1440,0),0)</f>
@@ -9315,16 +9315,16 @@
         <v/>
       </c>
       <c r="R102" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="S102" s="5" t="n">
         <v>0.6354166666666666</v>
       </c>
       <c r="T102" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.5</v>
       </c>
       <c r="U102" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="V102" s="3">
         <f>IF(COUNT(T102:U102)=2,ROUND((U102-T102)*1440,0),0)</f>
@@ -9487,16 +9487,16 @@
         <v/>
       </c>
       <c r="R104" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S104" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="T104" s="5" t="n">
-        <v>0.5625</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="U104" s="5" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.625</v>
       </c>
       <c r="V104" s="3">
         <f>IF(COUNT(T104:U104)=2,ROUND((U104-T104)*1440,0),0)</f>
@@ -9578,13 +9578,13 @@
         <v>0.4583333333333333</v>
       </c>
       <c r="S105" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="T105" s="5" t="n">
-        <v>0.5625</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="U105" s="5" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.625</v>
       </c>
       <c r="V105" s="3">
         <f>IF(COUNT(T105:U105)=2,ROUND((U105-T105)*1440,0),0)</f>
@@ -9663,16 +9663,16 @@
         <v/>
       </c>
       <c r="R106" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S106" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="T106" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="U106" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="V106" s="3">
         <f>IF(COUNT(T106:U106)=2,ROUND((U106-T106)*1440,0),0)</f>
@@ -9751,16 +9751,16 @@
         <v/>
       </c>
       <c r="R107" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S107" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="T107" s="5" t="n">
+        <v>0.5520833333333334</v>
+      </c>
+      <c r="U107" s="5" t="n">
         <v>0.59375</v>
-      </c>
-      <c r="U107" s="5" t="n">
-        <v>0.6354166666666666</v>
       </c>
       <c r="V107" s="3">
         <f>IF(COUNT(T107:U107)=2,ROUND((U107-T107)*1440,0),0)</f>
@@ -9839,16 +9839,16 @@
         <v/>
       </c>
       <c r="R108" s="5" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S108" s="5" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.6875</v>
       </c>
       <c r="T108" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.5625</v>
       </c>
       <c r="U108" s="5" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="V108" s="3">
         <f>IF(COUNT(T108:U108)=2,ROUND((U108-T108)*1440,0),0)</f>
@@ -10006,13 +10006,13 @@
         <v>0.4270833333333333</v>
       </c>
       <c r="S110" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="T110" s="5" t="n">
+        <v>0.5104166666666666</v>
+      </c>
+      <c r="U110" s="5" t="n">
         <v>0.5520833333333334</v>
-      </c>
-      <c r="U110" s="5" t="n">
-        <v>0.59375</v>
       </c>
       <c r="V110" s="3">
         <f>IF(COUNT(T110:U110)=2,ROUND((U110-T110)*1440,0),0)</f>
@@ -10255,16 +10255,16 @@
         <v/>
       </c>
       <c r="R113" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="S113" s="5" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="T113" s="5" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="U113" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.65625</v>
       </c>
       <c r="V113" s="3">
         <f>IF(COUNT(T113:U113)=2,ROUND((U113-T113)*1440,0),0)</f>
@@ -10343,16 +10343,16 @@
         <v/>
       </c>
       <c r="R114" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="S114" s="5" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="T114" s="5" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="U114" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.65625</v>
       </c>
       <c r="V114" s="3">
         <f>IF(COUNT(T114:U114)=2,ROUND((U114-T114)*1440,0),0)</f>
@@ -10431,16 +10431,16 @@
         <v/>
       </c>
       <c r="R115" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.53125</v>
       </c>
       <c r="S115" s="5" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="T115" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="U115" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="V115" s="3">
         <f>IF(COUNT(T115:U115)=2,ROUND((U115-T115)*1440,0),0)</f>
@@ -10519,16 +10519,16 @@
         <v/>
       </c>
       <c r="R116" s="5" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.5625</v>
       </c>
       <c r="S116" s="5" t="n">
-        <v>0.78125</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="T116" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="U116" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.71875</v>
       </c>
       <c r="V116" s="3">
         <f>IF(COUNT(T116:U116)=2,ROUND((U116-T116)*1440,0),0)</f>
@@ -10610,13 +10610,13 @@
         <v>0.5520833333333334</v>
       </c>
       <c r="S117" s="5" t="n">
-        <v>0.78125</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="T117" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="U117" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="V117" s="3">
         <f>IF(COUNT(T117:U117)=2,ROUND((U117-T117)*1440,0),0)</f>
@@ -10847,16 +10847,16 @@
         <v/>
       </c>
       <c r="R120" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="S120" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="T120" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="U120" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="V120" s="3">
         <f>IF(COUNT(T120:U120)=2,ROUND((U120-T120)*1440,0),0)</f>
@@ -10935,16 +10935,16 @@
         <v/>
       </c>
       <c r="R121" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="S121" s="5" t="n">
         <v>0.6354166666666666</v>
       </c>
       <c r="T121" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="U121" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.53125</v>
       </c>
       <c r="V121" s="3">
         <f>IF(COUNT(T121:U121)=2,ROUND((U121-T121)*1440,0),0)</f>
@@ -11023,7 +11023,7 @@
         <v/>
       </c>
       <c r="R122" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="S122" s="5" t="n">
         <v>0.6354166666666666</v>
@@ -11111,16 +11111,16 @@
         <v/>
       </c>
       <c r="R123" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="S123" s="5" t="n">
         <v>0.6354166666666666</v>
       </c>
       <c r="T123" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="U123" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="V123" s="3">
         <f>IF(COUNT(T123:U123)=2,ROUND((U123-T123)*1440,0),0)</f>
@@ -11283,16 +11283,16 @@
         <v/>
       </c>
       <c r="R125" s="5" t="n">
-        <v>0.5</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S125" s="5" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.71875</v>
       </c>
       <c r="T125" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="U125" s="5" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.59375</v>
       </c>
       <c r="V125" s="3">
         <f>IF(COUNT(T125:U125)=2,ROUND((U125-T125)*1440,0),0)</f>
@@ -11371,16 +11371,16 @@
         <v/>
       </c>
       <c r="R126" s="5" t="n">
-        <v>0.5</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S126" s="5" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.71875</v>
       </c>
       <c r="T126" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="U126" s="5" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.59375</v>
       </c>
       <c r="V126" s="3">
         <f>IF(COUNT(T126:U126)=2,ROUND((U126-T126)*1440,0),0)</f>
@@ -11462,13 +11462,13 @@
         <v>0.4583333333333333</v>
       </c>
       <c r="S127" s="5" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="T127" s="5" t="n">
+        <v>0.5104166666666666</v>
+      </c>
+      <c r="U127" s="5" t="n">
         <v>0.5520833333333334</v>
-      </c>
-      <c r="U127" s="5" t="n">
-        <v>0.59375</v>
       </c>
       <c r="V127" s="3">
         <f>IF(COUNT(T127:U127)=2,ROUND((U127-T127)*1440,0),0)</f>
@@ -11547,16 +11547,16 @@
         <v/>
       </c>
       <c r="R128" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S128" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="T128" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="U128" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="V128" s="3">
         <f>IF(COUNT(T128:U128)=2,ROUND((U128-T128)*1440,0),0)</f>
@@ -11638,7 +11638,7 @@
         <v>0.4583333333333333</v>
       </c>
       <c r="S129" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="T129" s="5" t="n">
         <v>0.5520833333333334</v>
@@ -11802,7 +11802,7 @@
         <v>0.4791666666666667</v>
       </c>
       <c r="S131" s="5" t="n">
-        <v>0.7395833333333334</v>
+        <v>0.75</v>
       </c>
       <c r="T131" s="5" t="n">
         <v>0.6145833333333334</v>
@@ -11887,16 +11887,16 @@
         <v/>
       </c>
       <c r="R132" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="S132" s="5" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.75</v>
       </c>
       <c r="T132" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="U132" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.65625</v>
       </c>
       <c r="V132" s="3">
         <f>IF(COUNT(T132:U132)=2,ROUND((U132-T132)*1440,0),0)</f>
@@ -12063,16 +12063,16 @@
         <v/>
       </c>
       <c r="R134" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="S134" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="T134" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="U134" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
       <c r="V134" s="3">
         <f>IF(COUNT(T134:U134)=2,ROUND((U134-T134)*1440,0),0)</f>
@@ -12151,7 +12151,7 @@
         <v/>
       </c>
       <c r="R135" s="5" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="S135" s="5" t="n">
         <v>0.71875</v>
@@ -12315,16 +12315,16 @@
         <v/>
       </c>
       <c r="R137" s="5" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S137" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.6875</v>
       </c>
       <c r="T137" s="5" t="n">
+        <v>0.5520833333333334</v>
+      </c>
+      <c r="U137" s="5" t="n">
         <v>0.59375</v>
-      </c>
-      <c r="U137" s="5" t="n">
-        <v>0.6354166666666666</v>
       </c>
       <c r="V137" s="3">
         <f>IF(COUNT(T137:U137)=2,ROUND((U137-T137)*1440,0),0)</f>
@@ -12403,7 +12403,7 @@
         <v/>
       </c>
       <c r="R138" s="5" t="n">
-        <v>0.5</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S138" s="5" t="n">
         <v>0.71875</v>
@@ -12743,16 +12743,16 @@
         <v/>
       </c>
       <c r="R142" s="5" t="n">
-        <v>0.5625</v>
+        <v>0.5729166666666666</v>
       </c>
       <c r="S142" s="5" t="n">
-        <v>0.78125</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="T142" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="U142" s="5" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="V142" s="3">
         <f>IF(COUNT(T142:U142)=2,ROUND((U142-T142)*1440,0),0)</f>
@@ -12834,13 +12834,13 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="S143" s="5" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="T143" s="5" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="U143" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.6875</v>
       </c>
       <c r="V143" s="3">
         <f>IF(COUNT(T143:U143)=2,ROUND((U143-T143)*1440,0),0)</f>
@@ -12922,13 +12922,13 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="S144" s="5" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="T144" s="5" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="U144" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.6875</v>
       </c>
       <c r="V144" s="3">
         <f>IF(COUNT(T144:U144)=2,ROUND((U144-T144)*1440,0),0)</f>
@@ -13170,13 +13170,13 @@
         <v>0.4270833333333333</v>
       </c>
       <c r="S147" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="T147" s="5" t="n">
+        <v>0.5104166666666666</v>
+      </c>
+      <c r="U147" s="5" t="n">
         <v>0.5520833333333334</v>
-      </c>
-      <c r="U147" s="5" t="n">
-        <v>0.59375</v>
       </c>
       <c r="V147" s="3">
         <f>IF(COUNT(T147:U147)=2,ROUND((U147-T147)*1440,0),0)</f>
@@ -13255,7 +13255,7 @@
         <v/>
       </c>
       <c r="R148" s="5" t="n">
-        <v>0.4375</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="S148" s="5" t="n">
         <v>0.6875</v>
@@ -13343,16 +13343,16 @@
         <v/>
       </c>
       <c r="R149" s="5" t="n">
-        <v>0.4375</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="S149" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="T149" s="5" t="n">
-        <v>0.53125</v>
+        <v>0.5625</v>
       </c>
       <c r="U149" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="V149" s="3">
         <f>IF(COUNT(T149:U149)=2,ROUND((U149-T149)*1440,0),0)</f>
@@ -13431,7 +13431,7 @@
         <v/>
       </c>
       <c r="R150" s="5" t="n">
-        <v>0.4375</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="S150" s="5" t="n">
         <v>0.6770833333333334</v>
@@ -13595,16 +13595,16 @@
         <v/>
       </c>
       <c r="R152" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="S152" s="5" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="T152" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.625</v>
       </c>
       <c r="U152" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="V152" s="3">
         <f>IF(COUNT(T152:U152)=2,ROUND((U152-T152)*1440,0),0)</f>
@@ -13683,16 +13683,16 @@
         <v/>
       </c>
       <c r="R153" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="S153" s="5" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="T153" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.625</v>
       </c>
       <c r="U153" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="V153" s="3">
         <f>IF(COUNT(T153:U153)=2,ROUND((U153-T153)*1440,0),0)</f>
@@ -13771,7 +13771,7 @@
         <v/>
       </c>
       <c r="R154" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="S154" s="5" t="n">
         <v>0.71875</v>
@@ -13859,10 +13859,10 @@
         <v/>
       </c>
       <c r="R155" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="S155" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="T155" s="5" t="n">
         <v>0.5520833333333334</v>
@@ -13947,16 +13947,16 @@
         <v/>
       </c>
       <c r="R156" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="S156" s="5" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.71875</v>
       </c>
       <c r="T156" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.59375</v>
       </c>
       <c r="U156" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="V156" s="3">
         <f>IF(COUNT(T156:U156)=2,ROUND((U156-T156)*1440,0),0)</f>
@@ -14111,16 +14111,16 @@
         <v/>
       </c>
       <c r="R158" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="S158" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.65625</v>
       </c>
       <c r="T158" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="U158" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.53125</v>
       </c>
       <c r="V158" s="3">
         <f>IF(COUNT(T158:U158)=2,ROUND((U158-T158)*1440,0),0)</f>
@@ -14199,16 +14199,16 @@
         <v/>
       </c>
       <c r="R159" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="S159" s="5" t="n">
         <v>0.65625</v>
       </c>
       <c r="T159" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="U159" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.53125</v>
       </c>
       <c r="V159" s="3">
         <f>IF(COUNT(T159:U159)=2,ROUND((U159-T159)*1440,0),0)</f>
@@ -14287,16 +14287,16 @@
         <v/>
       </c>
       <c r="R160" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="S160" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="T160" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.5</v>
       </c>
       <c r="U160" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="V160" s="3">
         <f>IF(COUNT(T160:U160)=2,ROUND((U160-T160)*1440,0),0)</f>
@@ -14375,7 +14375,7 @@
         <v/>
       </c>
       <c r="R161" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="S161" s="5" t="n">
         <v>0.6354166666666666</v>
@@ -14463,16 +14463,16 @@
         <v/>
       </c>
       <c r="R162" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="S162" s="5" t="n">
         <v>0.6354166666666666</v>
       </c>
       <c r="T162" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="U162" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="V162" s="3">
         <f>IF(COUNT(T162:U162)=2,ROUND((U162-T162)*1440,0),0)</f>
@@ -14627,16 +14627,16 @@
         <v/>
       </c>
       <c r="R164" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="S164" s="5" t="n">
         <v>0.6354166666666666</v>
       </c>
       <c r="T164" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.5</v>
       </c>
       <c r="U164" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="V164" s="3">
         <f>IF(COUNT(T164:U164)=2,ROUND((U164-T164)*1440,0),0)</f>
@@ -14715,16 +14715,16 @@
         <v/>
       </c>
       <c r="R165" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="S165" s="5" t="n">
         <v>0.6354166666666666</v>
       </c>
       <c r="T165" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.5</v>
       </c>
       <c r="U165" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="V165" s="3">
         <f>IF(COUNT(T165:U165)=2,ROUND((U165-T165)*1440,0),0)</f>
@@ -14890,13 +14890,13 @@
         <v>0.4583333333333333</v>
       </c>
       <c r="S167" s="5" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="T167" s="5" t="n">
+        <v>0.5520833333333334</v>
+      </c>
+      <c r="U167" s="5" t="n">
         <v>0.59375</v>
-      </c>
-      <c r="U167" s="5" t="n">
-        <v>0.6354166666666666</v>
       </c>
       <c r="V167" s="3">
         <f>IF(COUNT(T167:U167)=2,ROUND((U167-T167)*1440,0),0)</f>
@@ -14978,13 +14978,13 @@
         <v>0.4583333333333333</v>
       </c>
       <c r="S168" s="5" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="T168" s="5" t="n">
+        <v>0.5520833333333334</v>
+      </c>
+      <c r="U168" s="5" t="n">
         <v>0.59375</v>
-      </c>
-      <c r="U168" s="5" t="n">
-        <v>0.6354166666666666</v>
       </c>
       <c r="V168" s="3">
         <f>IF(COUNT(T168:U168)=2,ROUND((U168-T168)*1440,0),0)</f>
@@ -15066,13 +15066,13 @@
         <v>0.4583333333333333</v>
       </c>
       <c r="S169" s="5" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.71875</v>
       </c>
       <c r="T169" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.59375</v>
       </c>
       <c r="U169" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="V169" s="3">
         <f>IF(COUNT(T169:U169)=2,ROUND((U169-T169)*1440,0),0)</f>
@@ -15151,16 +15151,16 @@
         <v/>
       </c>
       <c r="R170" s="5" t="n">
-        <v>0.5</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S170" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="T170" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="U170" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="V170" s="3">
         <f>IF(COUNT(T170:U170)=2,ROUND((U170-T170)*1440,0),0)</f>
@@ -15239,7 +15239,7 @@
         <v/>
       </c>
       <c r="R171" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S171" s="5" t="n">
         <v>0.71875</v>
@@ -15479,16 +15479,16 @@
         <v/>
       </c>
       <c r="R174" s="5" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="S174" s="5" t="n">
-        <v>0.78125</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="T174" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="U174" s="5" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.71875</v>
       </c>
       <c r="V174" s="3">
         <f>IF(COUNT(T174:U174)=2,ROUND((U174-T174)*1440,0),0)</f>
@@ -15567,16 +15567,16 @@
         <v/>
       </c>
       <c r="R175" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="S175" s="5" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="T175" s="5" t="n">
+        <v>0.6354166666666666</v>
+      </c>
+      <c r="U175" s="5" t="n">
         <v>0.6770833333333334</v>
-      </c>
-      <c r="U175" s="5" t="n">
-        <v>0.71875</v>
       </c>
       <c r="V175" s="3">
         <f>IF(COUNT(T175:U175)=2,ROUND((U175-T175)*1440,0),0)</f>
@@ -15655,16 +15655,16 @@
         <v/>
       </c>
       <c r="R176" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.53125</v>
       </c>
       <c r="S176" s="5" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.78125</v>
       </c>
       <c r="T176" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.65625</v>
       </c>
       <c r="U176" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="V176" s="3">
         <f>IF(COUNT(T176:U176)=2,ROUND((U176-T176)*1440,0),0)</f>
@@ -15746,13 +15746,13 @@
         <v>0.5416666666666666</v>
       </c>
       <c r="S177" s="5" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="T177" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="U177" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.71875</v>
       </c>
       <c r="V177" s="3">
         <f>IF(COUNT(T177:U177)=2,ROUND((U177-T177)*1440,0),0)</f>
@@ -15907,10 +15907,10 @@
         <v/>
       </c>
       <c r="R179" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="S179" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.65625</v>
       </c>
       <c r="T179" s="5" t="n">
         <v>0.5104166666666666</v>
@@ -15995,10 +15995,10 @@
         <v/>
       </c>
       <c r="R180" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="S180" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.65625</v>
       </c>
       <c r="T180" s="5" t="n">
         <v>0.5104166666666666</v>
@@ -16086,13 +16086,13 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="S181" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="T181" s="5" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="U181" s="5" t="n">
         <v>0.5104166666666666</v>
-      </c>
-      <c r="U181" s="5" t="n">
-        <v>0.5520833333333334</v>
       </c>
       <c r="V181" s="3">
         <f>IF(COUNT(T181:U181)=2,ROUND((U181-T181)*1440,0),0)</f>
@@ -16171,16 +16171,16 @@
         <v/>
       </c>
       <c r="R182" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="S182" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="T182" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="U182" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.53125</v>
       </c>
       <c r="V182" s="3">
         <f>IF(COUNT(T182:U182)=2,ROUND((U182-T182)*1440,0),0)</f>
@@ -16259,16 +16259,16 @@
         <v/>
       </c>
       <c r="R183" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="S183" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="T183" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="U183" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.53125</v>
       </c>
       <c r="V183" s="3">
         <f>IF(COUNT(T183:U183)=2,ROUND((U183-T183)*1440,0),0)</f>
@@ -16431,16 +16431,16 @@
         <v/>
       </c>
       <c r="R185" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="S185" s="5" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.6875</v>
       </c>
       <c r="T185" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="U185" s="5" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.5625</v>
       </c>
       <c r="V185" s="3">
         <f>IF(COUNT(T185:U185)=2,ROUND((U185-T185)*1440,0),0)</f>
@@ -16519,16 +16519,16 @@
         <v/>
       </c>
       <c r="R186" s="5" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.46875</v>
       </c>
       <c r="S186" s="5" t="n">
-        <v>0.7395833333333334</v>
+        <v>0.6875</v>
       </c>
       <c r="T186" s="5" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="U186" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.5625</v>
       </c>
       <c r="V186" s="3">
         <f>IF(COUNT(T186:U186)=2,ROUND((U186-T186)*1440,0),0)</f>
@@ -16607,16 +16607,16 @@
         <v/>
       </c>
       <c r="R187" s="5" t="n">
-        <v>0.5</v>
+        <v>0.46875</v>
       </c>
       <c r="S187" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.6875</v>
       </c>
       <c r="T187" s="5" t="n">
+        <v>0.5520833333333334</v>
+      </c>
+      <c r="U187" s="5" t="n">
         <v>0.59375</v>
-      </c>
-      <c r="U187" s="5" t="n">
-        <v>0.6354166666666666</v>
       </c>
       <c r="V187" s="3">
         <f>IF(COUNT(T187:U187)=2,ROUND((U187-T187)*1440,0),0)</f>
@@ -16698,13 +16698,13 @@
         <v>0.4791666666666667</v>
       </c>
       <c r="S188" s="5" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="T188" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.5625</v>
       </c>
       <c r="U188" s="5" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="V188" s="3">
         <f>IF(COUNT(T188:U188)=2,ROUND((U188-T188)*1440,0),0)</f>
@@ -16786,13 +16786,13 @@
         <v>0.4583333333333333</v>
       </c>
       <c r="S189" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="T189" s="5" t="n">
+        <v>0.5104166666666666</v>
+      </c>
+      <c r="U189" s="5" t="n">
         <v>0.5520833333333334</v>
-      </c>
-      <c r="U189" s="5" t="n">
-        <v>0.59375</v>
       </c>
       <c r="V189" s="3">
         <f>IF(COUNT(T189:U189)=2,ROUND((U189-T189)*1440,0),0)</f>
@@ -16947,7 +16947,7 @@
         <v/>
       </c>
       <c r="R191" s="5" t="n">
-        <v>0.5</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S191" s="5" t="n">
         <v>0.71875</v>
@@ -17035,16 +17035,16 @@
         <v/>
       </c>
       <c r="R192" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S192" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.65625</v>
       </c>
       <c r="T192" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.53125</v>
       </c>
       <c r="U192" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.5729166666666666</v>
       </c>
       <c r="V192" s="3">
         <f>IF(COUNT(T192:U192)=2,ROUND((U192-T192)*1440,0),0)</f>
@@ -17199,16 +17199,16 @@
         <v/>
       </c>
       <c r="R194" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.5</v>
       </c>
       <c r="S194" s="5" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="T194" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="U194" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="V194" s="3">
         <f>IF(COUNT(T194:U194)=2,ROUND((U194-T194)*1440,0),0)</f>
@@ -17287,16 +17287,16 @@
         <v/>
       </c>
       <c r="R195" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.5</v>
       </c>
       <c r="S195" s="5" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="T195" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="U195" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="V195" s="3">
         <f>IF(COUNT(T195:U195)=2,ROUND((U195-T195)*1440,0),0)</f>
@@ -17375,16 +17375,16 @@
         <v/>
       </c>
       <c r="R196" s="5" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S196" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="T196" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="U196" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="V196" s="3">
         <f>IF(COUNT(T196:U196)=2,ROUND((U196-T196)*1440,0),0)</f>
@@ -17463,7 +17463,7 @@
         <v/>
       </c>
       <c r="R197" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S197" s="5" t="n">
         <v>0.71875</v>
@@ -17551,16 +17551,16 @@
         <v/>
       </c>
       <c r="R198" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S198" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="T198" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="U198" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="V198" s="3">
         <f>IF(COUNT(T198:U198)=2,ROUND((U198-T198)*1440,0),0)</f>
@@ -17879,16 +17879,16 @@
         <v/>
       </c>
       <c r="R202" s="5" t="n">
-        <v>0.5625</v>
+        <v>0.5729166666666666</v>
       </c>
       <c r="S202" s="5" t="n">
-        <v>0.78125</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="T202" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="U202" s="5" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="V202" s="3">
         <f>IF(COUNT(T202:U202)=2,ROUND((U202-T202)*1440,0),0)</f>
@@ -17970,13 +17970,13 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="S203" s="5" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="T203" s="5" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="U203" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.6875</v>
       </c>
       <c r="V203" s="3">
         <f>IF(COUNT(T203:U203)=2,ROUND((U203-T203)*1440,0),0)</f>
@@ -18058,13 +18058,13 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="S204" s="5" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="T204" s="5" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="U204" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.6875</v>
       </c>
       <c r="V204" s="3">
         <f>IF(COUNT(T204:U204)=2,ROUND((U204-T204)*1440,0),0)</f>
@@ -18227,16 +18227,16 @@
         <v/>
       </c>
       <c r="R206" s="5" t="n">
-        <v>0.4479166666666667</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="S206" s="5" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="T206" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="U206" s="5" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.5625</v>
       </c>
       <c r="V206" s="3">
         <f>IF(COUNT(T206:U206)=2,ROUND((U206-T206)*1440,0),0)</f>
@@ -18315,16 +18315,16 @@
         <v/>
       </c>
       <c r="R207" s="5" t="n">
-        <v>0.4479166666666667</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="S207" s="5" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="T207" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="U207" s="5" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.5625</v>
       </c>
       <c r="V207" s="3">
         <f>IF(COUNT(T207:U207)=2,ROUND((U207-T207)*1440,0),0)</f>
@@ -18403,16 +18403,16 @@
         <v/>
       </c>
       <c r="R208" s="5" t="n">
-        <v>0.4270833333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="S208" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="T208" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5729166666666666</v>
       </c>
       <c r="U208" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="V208" s="3">
         <f>IF(COUNT(T208:U208)=2,ROUND((U208-T208)*1440,0),0)</f>
@@ -18494,13 +18494,13 @@
         <v>0.4270833333333333</v>
       </c>
       <c r="S209" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="T209" s="5" t="n">
+        <v>0.5104166666666666</v>
+      </c>
+      <c r="U209" s="5" t="n">
         <v>0.5520833333333334</v>
-      </c>
-      <c r="U209" s="5" t="n">
-        <v>0.59375</v>
       </c>
       <c r="V209" s="3">
         <f>IF(COUNT(T209:U209)=2,ROUND((U209-T209)*1440,0),0)</f>
@@ -18743,10 +18743,10 @@
         <v/>
       </c>
       <c r="R212" s="5" t="n">
-        <v>0.4270833333333333</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="S212" s="5" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="T212" s="5" t="n">
         <v>0.5520833333333334</v>
@@ -18831,16 +18831,16 @@
         <v/>
       </c>
       <c r="R213" s="5" t="n">
-        <v>0.4375</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="S213" s="5" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="T213" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="U213" s="5" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.59375</v>
       </c>
       <c r="V213" s="3">
         <f>IF(COUNT(T213:U213)=2,ROUND((U213-T213)*1440,0),0)</f>
@@ -18919,16 +18919,16 @@
         <v/>
       </c>
       <c r="R214" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="S214" s="5" t="n">
         <v>0.6458333333333334</v>
       </c>
       <c r="T214" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="U214" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="V214" s="3">
         <f>IF(COUNT(T214:U214)=2,ROUND((U214-T214)*1440,0),0)</f>
@@ -19010,13 +19010,13 @@
         <v>0.4270833333333333</v>
       </c>
       <c r="S215" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="T215" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="U215" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="V215" s="3">
         <f>IF(COUNT(T215:U215)=2,ROUND((U215-T215)*1440,0),0)</f>
@@ -19095,16 +19095,16 @@
         <v/>
       </c>
       <c r="R216" s="5" t="n">
-        <v>0.4270833333333333</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="S216" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="T216" s="5" t="n">
-        <v>0.53125</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="U216" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="V216" s="3">
         <f>IF(COUNT(T216:U216)=2,ROUND((U216-T216)*1440,0),0)</f>
@@ -19259,16 +19259,16 @@
         <v/>
       </c>
       <c r="R218" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S218" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="T218" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="U218" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="V218" s="3">
         <f>IF(COUNT(T218:U218)=2,ROUND((U218-T218)*1440,0),0)</f>
@@ -19350,7 +19350,7 @@
         <v>0.4583333333333333</v>
       </c>
       <c r="S219" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="T219" s="5" t="n">
         <v>0.5520833333333334</v>
@@ -19511,16 +19511,16 @@
         <v/>
       </c>
       <c r="R221" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="S221" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="T221" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="U221" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="V221" s="3">
         <f>IF(COUNT(T221:U221)=2,ROUND((U221-T221)*1440,0),0)</f>
@@ -19599,16 +19599,16 @@
         <v/>
       </c>
       <c r="R222" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="S222" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="T222" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="U222" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="V222" s="3">
         <f>IF(COUNT(T222:U222)=2,ROUND((U222-T222)*1440,0),0)</f>
@@ -19687,16 +19687,16 @@
         <v/>
       </c>
       <c r="R223" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="S223" s="5" t="n">
         <v>0.6354166666666666</v>
       </c>
       <c r="T223" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="U223" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.53125</v>
       </c>
       <c r="V223" s="3">
         <f>IF(COUNT(T223:U223)=2,ROUND((U223-T223)*1440,0),0)</f>
@@ -19775,7 +19775,7 @@
         <v/>
       </c>
       <c r="R224" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="S224" s="5" t="n">
         <v>0.6354166666666666</v>
@@ -19863,16 +19863,16 @@
         <v/>
       </c>
       <c r="R225" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="S225" s="5" t="n">
         <v>0.6354166666666666</v>
       </c>
       <c r="T225" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="U225" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="V225" s="3">
         <f>IF(COUNT(T225:U225)=2,ROUND((U225-T225)*1440,0),0)</f>
@@ -20111,16 +20111,16 @@
         <v/>
       </c>
       <c r="R228" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="S228" s="5" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="T228" s="5" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="U228" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.65625</v>
       </c>
       <c r="V228" s="3">
         <f>IF(COUNT(T228:U228)=2,ROUND((U228-T228)*1440,0),0)</f>
@@ -20199,16 +20199,16 @@
         <v/>
       </c>
       <c r="R229" s="5" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.53125</v>
       </c>
       <c r="S229" s="5" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="T229" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="U229" s="5" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="V229" s="3">
         <f>IF(COUNT(T229:U229)=2,ROUND((U229-T229)*1440,0),0)</f>
@@ -20287,16 +20287,16 @@
         <v/>
       </c>
       <c r="R230" s="5" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.5625</v>
       </c>
       <c r="S230" s="5" t="n">
-        <v>0.78125</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="T230" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="U230" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.71875</v>
       </c>
       <c r="V230" s="3">
         <f>IF(COUNT(T230:U230)=2,ROUND((U230-T230)*1440,0),0)</f>
@@ -20378,13 +20378,13 @@
         <v>0.5520833333333334</v>
       </c>
       <c r="S231" s="5" t="n">
-        <v>0.78125</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="T231" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="U231" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="V231" s="3">
         <f>IF(COUNT(T231:U231)=2,ROUND((U231-T231)*1440,0),0)</f>
@@ -20539,16 +20539,16 @@
         <v/>
       </c>
       <c r="R233" s="5" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.46875</v>
       </c>
       <c r="S233" s="5" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.71875</v>
       </c>
       <c r="T233" s="5" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="U233" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="V233" s="3">
         <f>IF(COUNT(T233:U233)=2,ROUND((U233-T233)*1440,0),0)</f>
@@ -20627,16 +20627,16 @@
         <v/>
       </c>
       <c r="R234" s="5" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.46875</v>
       </c>
       <c r="S234" s="5" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.71875</v>
       </c>
       <c r="T234" s="5" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="U234" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="V234" s="3">
         <f>IF(COUNT(T234:U234)=2,ROUND((U234-T234)*1440,0),0)</f>
@@ -20715,16 +20715,16 @@
         <v/>
       </c>
       <c r="R235" s="5" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.46875</v>
       </c>
       <c r="S235" s="5" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="T235" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="U235" s="5" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.5625</v>
       </c>
       <c r="V235" s="3">
         <f>IF(COUNT(T235:U235)=2,ROUND((U235-T235)*1440,0),0)</f>
@@ -20803,16 +20803,16 @@
         <v/>
       </c>
       <c r="R236" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="S236" s="5" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.71875</v>
       </c>
       <c r="T236" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.59375</v>
       </c>
       <c r="U236" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="V236" s="3">
         <f>IF(COUNT(T236:U236)=2,ROUND((U236-T236)*1440,0),0)</f>
@@ -20891,16 +20891,16 @@
         <v/>
       </c>
       <c r="R237" s="5" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S237" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="T237" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="U237" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="V237" s="3">
         <f>IF(COUNT(T237:U237)=2,ROUND((U237-T237)*1440,0),0)</f>
@@ -21055,16 +21055,16 @@
         <v/>
       </c>
       <c r="R239" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="S239" s="5" t="n">
         <v>0.65625</v>
       </c>
       <c r="T239" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.53125</v>
       </c>
       <c r="U239" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5729166666666666</v>
       </c>
       <c r="V239" s="3">
         <f>IF(COUNT(T239:U239)=2,ROUND((U239-T239)*1440,0),0)</f>
@@ -21143,16 +21143,16 @@
         <v/>
       </c>
       <c r="R240" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="S240" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.65625</v>
       </c>
       <c r="T240" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.53125</v>
       </c>
       <c r="U240" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5729166666666666</v>
       </c>
       <c r="V240" s="3">
         <f>IF(COUNT(T240:U240)=2,ROUND((U240-T240)*1440,0),0)</f>
@@ -21231,16 +21231,16 @@
         <v/>
       </c>
       <c r="R241" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="S241" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.65625</v>
       </c>
       <c r="T241" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.53125</v>
       </c>
       <c r="U241" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5729166666666666</v>
       </c>
       <c r="V241" s="3">
         <f>IF(COUNT(T241:U241)=2,ROUND((U241-T241)*1440,0),0)</f>
@@ -21319,16 +21319,16 @@
         <v/>
       </c>
       <c r="R242" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="S242" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="T242" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="U242" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.53125</v>
       </c>
       <c r="V242" s="3">
         <f>IF(COUNT(T242:U242)=2,ROUND((U242-T242)*1440,0),0)</f>
@@ -21407,16 +21407,16 @@
         <v/>
       </c>
       <c r="R243" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="S243" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="T243" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="U243" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.53125</v>
       </c>
       <c r="V243" s="3">
         <f>IF(COUNT(T243:U243)=2,ROUND((U243-T243)*1440,0),0)</f>
@@ -21571,16 +21571,16 @@
         <v/>
       </c>
       <c r="R245" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="S245" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="T245" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="U245" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.53125</v>
       </c>
       <c r="V245" s="3">
         <f>IF(COUNT(T245:U245)=2,ROUND((U245-T245)*1440,0),0)</f>
@@ -21659,16 +21659,16 @@
         <v/>
       </c>
       <c r="R246" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="S246" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="T246" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="U246" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.53125</v>
       </c>
       <c r="V246" s="3">
         <f>IF(COUNT(T246:U246)=2,ROUND((U246-T246)*1440,0),0)</f>
@@ -21831,16 +21831,16 @@
         <v/>
       </c>
       <c r="R248" s="5" t="n">
-        <v>0.5</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S248" s="5" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="T248" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="U248" s="5" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.625</v>
       </c>
       <c r="V248" s="3">
         <f>IF(COUNT(T248:U248)=2,ROUND((U248-T248)*1440,0),0)</f>
@@ -21919,16 +21919,16 @@
         <v/>
       </c>
       <c r="R249" s="5" t="n">
-        <v>0.5</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S249" s="5" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="T249" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="U249" s="5" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.625</v>
       </c>
       <c r="V249" s="3">
         <f>IF(COUNT(T249:U249)=2,ROUND((U249-T249)*1440,0),0)</f>
@@ -22007,16 +22007,16 @@
         <v/>
       </c>
       <c r="R250" s="5" t="n">
-        <v>0.5</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S250" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="T250" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="U250" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="V250" s="3">
         <f>IF(COUNT(T250:U250)=2,ROUND((U250-T250)*1440,0),0)</f>
@@ -22095,16 +22095,16 @@
         <v/>
       </c>
       <c r="R251" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S251" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.6875</v>
       </c>
       <c r="T251" s="5" t="n">
+        <v>0.5520833333333334</v>
+      </c>
+      <c r="U251" s="5" t="n">
         <v>0.59375</v>
-      </c>
-      <c r="U251" s="5" t="n">
-        <v>0.6354166666666666</v>
       </c>
       <c r="V251" s="3">
         <f>IF(COUNT(T251:U251)=2,ROUND((U251-T251)*1440,0),0)</f>
@@ -22183,16 +22183,16 @@
         <v/>
       </c>
       <c r="R252" s="5" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S252" s="5" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.6875</v>
       </c>
       <c r="T252" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.5625</v>
       </c>
       <c r="U252" s="5" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="V252" s="3">
         <f>IF(COUNT(T252:U252)=2,ROUND((U252-T252)*1440,0),0)</f>
@@ -22423,16 +22423,16 @@
         <v/>
       </c>
       <c r="R255" s="5" t="n">
-        <v>0.5</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S255" s="5" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="T255" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="U255" s="5" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.625</v>
       </c>
       <c r="V255" s="3">
         <f>IF(COUNT(T255:U255)=2,ROUND((U255-T255)*1440,0),0)</f>
@@ -22511,16 +22511,16 @@
         <v/>
       </c>
       <c r="R256" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S256" s="5" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="T256" s="5" t="n">
-        <v>0.5625</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="U256" s="5" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="V256" s="3">
         <f>IF(COUNT(T256:U256)=2,ROUND((U256-T256)*1440,0),0)</f>
@@ -22599,16 +22599,16 @@
         <v/>
       </c>
       <c r="R257" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S257" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.6875</v>
       </c>
       <c r="T257" s="5" t="n">
+        <v>0.5520833333333334</v>
+      </c>
+      <c r="U257" s="5" t="n">
         <v>0.59375</v>
-      </c>
-      <c r="U257" s="5" t="n">
-        <v>0.6354166666666666</v>
       </c>
       <c r="V257" s="3">
         <f>IF(COUNT(T257:U257)=2,ROUND((U257-T257)*1440,0),0)</f>
@@ -22687,16 +22687,16 @@
         <v/>
       </c>
       <c r="R258" s="5" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S258" s="5" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.6875</v>
       </c>
       <c r="T258" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.5625</v>
       </c>
       <c r="U258" s="5" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="V258" s="3">
         <f>IF(COUNT(T258:U258)=2,ROUND((U258-T258)*1440,0),0)</f>
@@ -22851,7 +22851,7 @@
         <v/>
       </c>
       <c r="R260" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.5625</v>
       </c>
       <c r="S260" s="5" t="n">
         <v>0.7916666666666666</v>
@@ -22939,7 +22939,7 @@
         <v/>
       </c>
       <c r="R261" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.5625</v>
       </c>
       <c r="S261" s="5" t="n">
         <v>0.7916666666666666</v>
@@ -23118,13 +23118,13 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="S263" s="5" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="T263" s="5" t="n">
+        <v>0.6354166666666666</v>
+      </c>
+      <c r="U263" s="5" t="n">
         <v>0.6770833333333334</v>
-      </c>
-      <c r="U263" s="5" t="n">
-        <v>0.71875</v>
       </c>
       <c r="V263" s="3">
         <f>IF(COUNT(T263:U263)=2,ROUND((U263-T263)*1440,0),0)</f>
@@ -23206,13 +23206,13 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="S264" s="5" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="T264" s="5" t="n">
+        <v>0.6354166666666666</v>
+      </c>
+      <c r="U264" s="5" t="n">
         <v>0.6770833333333334</v>
-      </c>
-      <c r="U264" s="5" t="n">
-        <v>0.71875</v>
       </c>
       <c r="V264" s="3">
         <f>IF(COUNT(T264:U264)=2,ROUND((U264-T264)*1440,0),0)</f>
@@ -23375,16 +23375,16 @@
         <v/>
       </c>
       <c r="R266" s="5" t="n">
-        <v>0.4479166666666667</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="S266" s="5" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="T266" s="5" t="n">
+        <v>0.5104166666666666</v>
+      </c>
+      <c r="U266" s="5" t="n">
         <v>0.5520833333333334</v>
-      </c>
-      <c r="U266" s="5" t="n">
-        <v>0.59375</v>
       </c>
       <c r="V266" s="3">
         <f>IF(COUNT(T266:U266)=2,ROUND((U266-T266)*1440,0),0)</f>
@@ -23466,13 +23466,13 @@
         <v>0.4270833333333333</v>
       </c>
       <c r="S267" s="5" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="T267" s="5" t="n">
+        <v>0.5104166666666666</v>
+      </c>
+      <c r="U267" s="5" t="n">
         <v>0.5520833333333334</v>
-      </c>
-      <c r="U267" s="5" t="n">
-        <v>0.59375</v>
       </c>
       <c r="V267" s="3">
         <f>IF(COUNT(T267:U267)=2,ROUND((U267-T267)*1440,0),0)</f>
@@ -23551,10 +23551,10 @@
         <v/>
       </c>
       <c r="R268" s="5" t="n">
-        <v>0.4375</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="S268" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="T268" s="5" t="n">
         <v>0.5520833333333334</v>
@@ -23639,16 +23639,16 @@
         <v/>
       </c>
       <c r="R269" s="5" t="n">
-        <v>0.4375</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="S269" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="T269" s="5" t="n">
-        <v>0.53125</v>
+        <v>0.5729166666666666</v>
       </c>
       <c r="U269" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="V269" s="3">
         <f>IF(COUNT(T269:U269)=2,ROUND((U269-T269)*1440,0),0)</f>
@@ -23727,7 +23727,7 @@
         <v/>
       </c>
       <c r="R270" s="5" t="n">
-        <v>0.4375</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="S270" s="5" t="n">
         <v>0.6770833333333334</v>
@@ -23891,10 +23891,10 @@
         <v/>
       </c>
       <c r="R272" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="S272" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="T272" s="5" t="n">
         <v>0.5520833333333334</v>
@@ -23979,16 +23979,16 @@
         <v/>
       </c>
       <c r="R273" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="S273" s="5" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.71875</v>
       </c>
       <c r="T273" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.59375</v>
       </c>
       <c r="U273" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="V273" s="3">
         <f>IF(COUNT(T273:U273)=2,ROUND((U273-T273)*1440,0),0)</f>
@@ -24143,16 +24143,16 @@
         <v/>
       </c>
       <c r="R275" s="5" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="S275" s="5" t="n">
-        <v>0.7395833333333334</v>
+        <v>0.75</v>
       </c>
       <c r="T275" s="5" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.625</v>
       </c>
       <c r="U275" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="V275" s="3">
         <f>IF(COUNT(T275:U275)=2,ROUND((U275-T275)*1440,0),0)</f>
@@ -24231,16 +24231,16 @@
         <v/>
       </c>
       <c r="R276" s="5" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="S276" s="5" t="n">
-        <v>0.7395833333333334</v>
+        <v>0.75</v>
       </c>
       <c r="T276" s="5" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.625</v>
       </c>
       <c r="U276" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="V276" s="3">
         <f>IF(COUNT(T276:U276)=2,ROUND((U276-T276)*1440,0),0)</f>
@@ -24319,7 +24319,7 @@
         <v/>
       </c>
       <c r="R277" s="5" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="S277" s="5" t="n">
         <v>0.71875</v>
@@ -24407,16 +24407,16 @@
         <v/>
       </c>
       <c r="R278" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="S278" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="T278" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="U278" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
       <c r="V278" s="3">
         <f>IF(COUNT(T278:U278)=2,ROUND((U278-T278)*1440,0),0)</f>
@@ -24495,7 +24495,7 @@
         <v/>
       </c>
       <c r="R279" s="5" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="S279" s="5" t="n">
         <v>0.71875</v>
@@ -24735,10 +24735,10 @@
         <v/>
       </c>
       <c r="R282" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="S282" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.65625</v>
       </c>
       <c r="T282" s="5" t="n">
         <v>0.5104166666666666</v>
@@ -24823,16 +24823,16 @@
         <v/>
       </c>
       <c r="R283" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="S283" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.65625</v>
       </c>
       <c r="T283" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.53125</v>
       </c>
       <c r="U283" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5729166666666666</v>
       </c>
       <c r="V283" s="3">
         <f>IF(COUNT(T283:U283)=2,ROUND((U283-T283)*1440,0),0)</f>
@@ -24911,16 +24911,16 @@
         <v/>
       </c>
       <c r="R284" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="S284" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="T284" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="U284" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.53125</v>
       </c>
       <c r="V284" s="3">
         <f>IF(COUNT(T284:U284)=2,ROUND((U284-T284)*1440,0),0)</f>
@@ -24999,16 +24999,16 @@
         <v/>
       </c>
       <c r="R285" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="S285" s="5" t="n">
         <v>0.6354166666666666</v>
       </c>
       <c r="T285" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.5</v>
       </c>
       <c r="U285" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="V285" s="3">
         <f>IF(COUNT(T285:U285)=2,ROUND((U285-T285)*1440,0),0)</f>
@@ -25171,7 +25171,7 @@
         <v/>
       </c>
       <c r="R287" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="S287" s="5" t="n">
         <v>0.78125</v>
@@ -25259,7 +25259,7 @@
         <v/>
       </c>
       <c r="R288" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="S288" s="5" t="n">
         <v>0.78125</v>
@@ -25347,16 +25347,16 @@
         <v/>
       </c>
       <c r="R289" s="5" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="S289" s="5" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="T289" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="U289" s="5" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="V289" s="3">
         <f>IF(COUNT(T289:U289)=2,ROUND((U289-T289)*1440,0),0)</f>
@@ -25435,7 +25435,7 @@
         <v/>
       </c>
       <c r="R290" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.53125</v>
       </c>
       <c r="S290" s="5" t="n">
         <v>0.7708333333333334</v>
@@ -25523,16 +25523,16 @@
         <v/>
       </c>
       <c r="R291" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="S291" s="5" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.78125</v>
       </c>
       <c r="T291" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.65625</v>
       </c>
       <c r="U291" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="V291" s="3">
         <f>IF(COUNT(T291:U291)=2,ROUND((U291-T291)*1440,0),0)</f>
@@ -25687,7 +25687,7 @@
         <v/>
       </c>
       <c r="R293" s="5" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S293" s="5" t="n">
         <v>0.7291666666666666</v>
@@ -25775,16 +25775,16 @@
         <v/>
       </c>
       <c r="R294" s="5" t="n">
-        <v>0.5</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S294" s="5" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="T294" s="5" t="n">
+        <v>0.59375</v>
+      </c>
+      <c r="U294" s="5" t="n">
         <v>0.6354166666666666</v>
-      </c>
-      <c r="U294" s="5" t="n">
-        <v>0.6770833333333334</v>
       </c>
       <c r="V294" s="3">
         <f>IF(COUNT(T294:U294)=2,ROUND((U294-T294)*1440,0),0)</f>
@@ -25863,16 +25863,16 @@
         <v/>
       </c>
       <c r="R295" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="S295" s="5" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.71875</v>
       </c>
       <c r="T295" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.59375</v>
       </c>
       <c r="U295" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="V295" s="3">
         <f>IF(COUNT(T295:U295)=2,ROUND((U295-T295)*1440,0),0)</f>
@@ -25951,7 +25951,7 @@
         <v/>
       </c>
       <c r="R296" s="5" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S296" s="5" t="n">
         <v>0.71875</v>
@@ -26039,16 +26039,16 @@
         <v/>
       </c>
       <c r="R297" s="5" t="n">
-        <v>0.5</v>
+        <v>0.46875</v>
       </c>
       <c r="S297" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="T297" s="5" t="n">
+        <v>0.5520833333333334</v>
+      </c>
+      <c r="U297" s="5" t="n">
         <v>0.59375</v>
-      </c>
-      <c r="U297" s="5" t="n">
-        <v>0.6354166666666666</v>
       </c>
       <c r="V297" s="3">
         <f>IF(COUNT(T297:U297)=2,ROUND((U297-T297)*1440,0),0)</f>
@@ -26203,16 +26203,16 @@
         <v/>
       </c>
       <c r="R299" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="S299" s="5" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.71875</v>
       </c>
       <c r="T299" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.59375</v>
       </c>
       <c r="U299" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="V299" s="3">
         <f>IF(COUNT(T299:U299)=2,ROUND((U299-T299)*1440,0),0)</f>
@@ -26291,16 +26291,16 @@
         <v/>
       </c>
       <c r="R300" s="5" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S300" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="T300" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="U300" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="V300" s="3">
         <f>IF(COUNT(T300:U300)=2,ROUND((U300-T300)*1440,0),0)</f>
@@ -26455,10 +26455,10 @@
         <v/>
       </c>
       <c r="R302" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="S302" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.65625</v>
       </c>
       <c r="T302" s="5" t="n">
         <v>0.5104166666666666</v>
@@ -26543,10 +26543,10 @@
         <v/>
       </c>
       <c r="R303" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="S303" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.65625</v>
       </c>
       <c r="T303" s="5" t="n">
         <v>0.5104166666666666</v>
@@ -26631,16 +26631,16 @@
         <v/>
       </c>
       <c r="R304" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="S304" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.65625</v>
       </c>
       <c r="T304" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.53125</v>
       </c>
       <c r="U304" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5729166666666666</v>
       </c>
       <c r="V304" s="3">
         <f>IF(COUNT(T304:U304)=2,ROUND((U304-T304)*1440,0),0)</f>
@@ -26719,16 +26719,16 @@
         <v/>
       </c>
       <c r="R305" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="S305" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="T305" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="U305" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.53125</v>
       </c>
       <c r="V305" s="3">
         <f>IF(COUNT(T305:U305)=2,ROUND((U305-T305)*1440,0),0)</f>
@@ -26807,16 +26807,16 @@
         <v/>
       </c>
       <c r="R306" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="S306" s="5" t="n">
         <v>0.6354166666666666</v>
       </c>
       <c r="T306" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.5</v>
       </c>
       <c r="U306" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="V306" s="3">
         <f>IF(COUNT(T306:U306)=2,ROUND((U306-T306)*1440,0),0)</f>
@@ -27055,16 +27055,16 @@
         <v/>
       </c>
       <c r="R309" s="5" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="S309" s="5" t="n">
-        <v>0.7395833333333334</v>
+        <v>0.75</v>
       </c>
       <c r="T309" s="5" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.625</v>
       </c>
       <c r="U309" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="V309" s="3">
         <f>IF(COUNT(T309:U309)=2,ROUND((U309-T309)*1440,0),0)</f>
@@ -27143,7 +27143,7 @@
         <v/>
       </c>
       <c r="R310" s="5" t="n">
-        <v>0.5</v>
+        <v>0.46875</v>
       </c>
       <c r="S310" s="5" t="n">
         <v>0.71875</v>
@@ -27231,16 +27231,16 @@
         <v/>
       </c>
       <c r="R311" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="S311" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="T311" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="U311" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
       <c r="V311" s="3">
         <f>IF(COUNT(T311:U311)=2,ROUND((U311-T311)*1440,0),0)</f>
@@ -27319,7 +27319,7 @@
         <v/>
       </c>
       <c r="R312" s="5" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="S312" s="5" t="n">
         <v>0.71875</v>
@@ -27483,7 +27483,7 @@
         <v/>
       </c>
       <c r="R314" s="5" t="n">
-        <v>0.5625</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="S314" s="5" t="n">
         <v>0.8020833333333334</v>
@@ -27571,7 +27571,7 @@
         <v/>
       </c>
       <c r="R315" s="5" t="n">
-        <v>0.5625</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="S315" s="5" t="n">
         <v>0.8020833333333334</v>
@@ -27659,16 +27659,16 @@
         <v/>
       </c>
       <c r="R316" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5625</v>
       </c>
       <c r="S316" s="5" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="T316" s="5" t="n">
+        <v>0.6354166666666666</v>
+      </c>
+      <c r="U316" s="5" t="n">
         <v>0.6770833333333334</v>
-      </c>
-      <c r="U316" s="5" t="n">
-        <v>0.71875</v>
       </c>
       <c r="V316" s="3">
         <f>IF(COUNT(T316:U316)=2,ROUND((U316-T316)*1440,0),0)</f>
@@ -27747,16 +27747,16 @@
         <v/>
       </c>
       <c r="R317" s="5" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="S317" s="5" t="n">
-        <v>0.78125</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="T317" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="U317" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.71875</v>
       </c>
       <c r="V317" s="3">
         <f>IF(COUNT(T317:U317)=2,ROUND((U317-T317)*1440,0),0)</f>
@@ -27835,16 +27835,16 @@
         <v/>
       </c>
       <c r="R318" s="5" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5729166666666666</v>
       </c>
       <c r="S318" s="5" t="n">
-        <v>0.78125</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="T318" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="U318" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.71875</v>
       </c>
       <c r="V318" s="3">
         <f>IF(COUNT(T318:U318)=2,ROUND((U318-T318)*1440,0),0)</f>
@@ -28002,13 +28002,13 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="S320" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="T320" s="5" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="U320" s="5" t="n">
         <v>0.5104166666666666</v>
-      </c>
-      <c r="U320" s="5" t="n">
-        <v>0.5520833333333334</v>
       </c>
       <c r="V320" s="3">
         <f>IF(COUNT(T320:U320)=2,ROUND((U320-T320)*1440,0),0)</f>
@@ -28090,13 +28090,13 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="S321" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="T321" s="5" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="U321" s="5" t="n">
         <v>0.5104166666666666</v>
-      </c>
-      <c r="U321" s="5" t="n">
-        <v>0.5520833333333334</v>
       </c>
       <c r="V321" s="3">
         <f>IF(COUNT(T321:U321)=2,ROUND((U321-T321)*1440,0),0)</f>
@@ -28178,13 +28178,13 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="S322" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.59375</v>
       </c>
       <c r="T322" s="5" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="U322" s="5" t="n">
         <v>0.5104166666666666</v>
-      </c>
-      <c r="U322" s="5" t="n">
-        <v>0.5520833333333334</v>
       </c>
       <c r="V322" s="3">
         <f>IF(COUNT(T322:U322)=2,ROUND((U322-T322)*1440,0),0)</f>
@@ -28269,10 +28269,10 @@
         <v>0.6354166666666666</v>
       </c>
       <c r="T323" s="5" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="U323" s="5" t="n">
         <v>0.5104166666666666</v>
-      </c>
-      <c r="U323" s="5" t="n">
-        <v>0.5520833333333334</v>
       </c>
       <c r="V323" s="3">
         <f>IF(COUNT(T323:U323)=2,ROUND((U323-T323)*1440,0),0)</f>
@@ -28354,13 +28354,13 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="S324" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="T324" s="5" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="U324" s="5" t="n">
         <v>0.5104166666666666</v>
-      </c>
-      <c r="U324" s="5" t="n">
-        <v>0.5520833333333334</v>
       </c>
       <c r="V324" s="3">
         <f>IF(COUNT(T324:U324)=2,ROUND((U324-T324)*1440,0),0)</f>
@@ -28518,13 +28518,13 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="S326" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.59375</v>
       </c>
       <c r="T326" s="5" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="U326" s="5" t="n">
         <v>0.5104166666666666</v>
-      </c>
-      <c r="U326" s="5" t="n">
-        <v>0.5520833333333334</v>
       </c>
       <c r="V326" s="3">
         <f>IF(COUNT(T326:U326)=2,ROUND((U326-T326)*1440,0),0)</f>
@@ -28606,13 +28606,13 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="S327" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.59375</v>
       </c>
       <c r="T327" s="5" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="U327" s="5" t="n">
         <v>0.5104166666666666</v>
-      </c>
-      <c r="U327" s="5" t="n">
-        <v>0.5520833333333334</v>
       </c>
       <c r="V327" s="3">
         <f>IF(COUNT(T327:U327)=2,ROUND((U327-T327)*1440,0),0)</f>
@@ -28775,16 +28775,16 @@
         <v/>
       </c>
       <c r="R329" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="S329" s="5" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6875</v>
       </c>
       <c r="T329" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="U329" s="5" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.5625</v>
       </c>
       <c r="V329" s="3">
         <f>IF(COUNT(T329:U329)=2,ROUND((U329-T329)*1440,0),0)</f>
@@ -28863,16 +28863,16 @@
         <v/>
       </c>
       <c r="R330" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="S330" s="5" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6875</v>
       </c>
       <c r="T330" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="U330" s="5" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.5625</v>
       </c>
       <c r="V330" s="3">
         <f>IF(COUNT(T330:U330)=2,ROUND((U330-T330)*1440,0),0)</f>
@@ -28951,10 +28951,10 @@
         <v/>
       </c>
       <c r="R331" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="S331" s="5" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="T331" s="5" t="n">
         <v>0.5520833333333334</v>
@@ -29042,13 +29042,13 @@
         <v>0.4791666666666667</v>
       </c>
       <c r="S332" s="5" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="T332" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="U332" s="5" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.625</v>
       </c>
       <c r="V332" s="3">
         <f>IF(COUNT(T332:U332)=2,ROUND((U332-T332)*1440,0),0)</f>
@@ -29130,13 +29130,13 @@
         <v>0.4583333333333333</v>
       </c>
       <c r="S333" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.65625</v>
       </c>
       <c r="T333" s="5" t="n">
+        <v>0.5104166666666666</v>
+      </c>
+      <c r="U333" s="5" t="n">
         <v>0.5520833333333334</v>
-      </c>
-      <c r="U333" s="5" t="n">
-        <v>0.59375</v>
       </c>
       <c r="V333" s="3">
         <f>IF(COUNT(T333:U333)=2,ROUND((U333-T333)*1440,0),0)</f>
@@ -29367,16 +29367,16 @@
         <v/>
       </c>
       <c r="R336" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="S336" s="5" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6875</v>
       </c>
       <c r="T336" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="U336" s="5" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.5625</v>
       </c>
       <c r="V336" s="3">
         <f>IF(COUNT(T336:U336)=2,ROUND((U336-T336)*1440,0),0)</f>
@@ -29455,16 +29455,16 @@
         <v/>
       </c>
       <c r="R337" s="5" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.46875</v>
       </c>
       <c r="S337" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="T337" s="5" t="n">
+        <v>0.5520833333333334</v>
+      </c>
+      <c r="U337" s="5" t="n">
         <v>0.59375</v>
-      </c>
-      <c r="U337" s="5" t="n">
-        <v>0.6354166666666666</v>
       </c>
       <c r="V337" s="3">
         <f>IF(COUNT(T337:U337)=2,ROUND((U337-T337)*1440,0),0)</f>
@@ -29546,13 +29546,13 @@
         <v>0.4791666666666667</v>
       </c>
       <c r="S338" s="5" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="T338" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="U338" s="5" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.625</v>
       </c>
       <c r="V338" s="3">
         <f>IF(COUNT(T338:U338)=2,ROUND((U338-T338)*1440,0),0)</f>
@@ -29634,13 +29634,13 @@
         <v>0.4583333333333333</v>
       </c>
       <c r="S339" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.65625</v>
       </c>
       <c r="T339" s="5" t="n">
+        <v>0.5104166666666666</v>
+      </c>
+      <c r="U339" s="5" t="n">
         <v>0.5520833333333334</v>
-      </c>
-      <c r="U339" s="5" t="n">
-        <v>0.59375</v>
       </c>
       <c r="V339" s="3">
         <f>IF(COUNT(T339:U339)=2,ROUND((U339-T339)*1440,0),0)</f>
@@ -29795,16 +29795,16 @@
         <v/>
       </c>
       <c r="R341" s="5" t="n">
-        <v>0.4375</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="S341" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.59375</v>
       </c>
       <c r="T341" s="5" t="n">
-        <v>0.53125</v>
+        <v>0.46875</v>
       </c>
       <c r="U341" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="V341" s="3">
         <f>IF(COUNT(T341:U341)=2,ROUND((U341-T341)*1440,0),0)</f>
@@ -29883,16 +29883,16 @@
         <v/>
       </c>
       <c r="R342" s="5" t="n">
-        <v>0.4375</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="S342" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.59375</v>
       </c>
       <c r="T342" s="5" t="n">
-        <v>0.53125</v>
+        <v>0.46875</v>
       </c>
       <c r="U342" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="V342" s="3">
         <f>IF(COUNT(T342:U342)=2,ROUND((U342-T342)*1440,0),0)</f>
@@ -29974,13 +29974,13 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="S343" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="T343" s="5" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="U343" s="5" t="n">
         <v>0.5104166666666666</v>
-      </c>
-      <c r="U343" s="5" t="n">
-        <v>0.5520833333333334</v>
       </c>
       <c r="V343" s="3">
         <f>IF(COUNT(T343:U343)=2,ROUND((U343-T343)*1440,0),0)</f>
@@ -30062,13 +30062,13 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="S344" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.59375</v>
       </c>
       <c r="T344" s="5" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="U344" s="5" t="n">
         <v>0.5104166666666666</v>
-      </c>
-      <c r="U344" s="5" t="n">
-        <v>0.5520833333333334</v>
       </c>
       <c r="V344" s="3">
         <f>IF(COUNT(T344:U344)=2,ROUND((U344-T344)*1440,0),0)</f>
@@ -30150,13 +30150,13 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="S345" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.59375</v>
       </c>
       <c r="T345" s="5" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="U345" s="5" t="n">
         <v>0.5104166666666666</v>
-      </c>
-      <c r="U345" s="5" t="n">
-        <v>0.5520833333333334</v>
       </c>
       <c r="V345" s="3">
         <f>IF(COUNT(T345:U345)=2,ROUND((U345-T345)*1440,0),0)</f>
@@ -30319,16 +30319,16 @@
         <v/>
       </c>
       <c r="R347" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="S347" s="5" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="T347" s="5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="U347" s="5" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.71875</v>
       </c>
       <c r="V347" s="3">
         <f>IF(COUNT(T347:U347)=2,ROUND((U347-T347)*1440,0),0)</f>
@@ -30407,16 +30407,16 @@
         <v/>
       </c>
       <c r="R348" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="S348" s="5" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="T348" s="5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="U348" s="5" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.71875</v>
       </c>
       <c r="V348" s="3">
         <f>IF(COUNT(T348:U348)=2,ROUND((U348-T348)*1440,0),0)</f>
@@ -30495,16 +30495,16 @@
         <v/>
       </c>
       <c r="R349" s="5" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="S349" s="5" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="T349" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="U349" s="5" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.71875</v>
       </c>
       <c r="V349" s="3">
         <f>IF(COUNT(T349:U349)=2,ROUND((U349-T349)*1440,0),0)</f>
@@ -30583,16 +30583,16 @@
         <v/>
       </c>
       <c r="R350" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.53125</v>
       </c>
       <c r="S350" s="5" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.78125</v>
       </c>
       <c r="T350" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.65625</v>
       </c>
       <c r="U350" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="V350" s="3">
         <f>IF(COUNT(T350:U350)=2,ROUND((U350-T350)*1440,0),0)</f>
@@ -30671,7 +30671,7 @@
         <v/>
       </c>
       <c r="R351" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="S351" s="5" t="n">
         <v>0.7708333333333334</v>
@@ -30835,16 +30835,16 @@
         <v/>
       </c>
       <c r="R353" s="5" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S353" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="T353" s="5" t="n">
+        <v>0.5520833333333334</v>
+      </c>
+      <c r="U353" s="5" t="n">
         <v>0.59375</v>
-      </c>
-      <c r="U353" s="5" t="n">
-        <v>0.6354166666666666</v>
       </c>
       <c r="V353" s="3">
         <f>IF(COUNT(T353:U353)=2,ROUND((U353-T353)*1440,0),0)</f>
@@ -30923,7 +30923,7 @@
         <v/>
       </c>
       <c r="R354" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="S354" s="5" t="n">
         <v>0.7083333333333334</v>
@@ -31087,16 +31087,16 @@
         <v/>
       </c>
       <c r="R356" s="5" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S356" s="5" t="n">
-        <v>0.75</v>
+        <v>0.71875</v>
       </c>
       <c r="T356" s="5" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="U356" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.59375</v>
       </c>
       <c r="V356" s="3">
         <f>IF(COUNT(T356:U356)=2,ROUND((U356-T356)*1440,0),0)</f>
@@ -31175,16 +31175,16 @@
         <v/>
       </c>
       <c r="R357" s="5" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S357" s="5" t="n">
-        <v>0.75</v>
+        <v>0.71875</v>
       </c>
       <c r="T357" s="5" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="U357" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.59375</v>
       </c>
       <c r="V357" s="3">
         <f>IF(COUNT(T357:U357)=2,ROUND((U357-T357)*1440,0),0)</f>
@@ -31263,16 +31263,16 @@
         <v/>
       </c>
       <c r="R358" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="S358" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="T358" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="U358" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.625</v>
       </c>
       <c r="V358" s="3">
         <f>IF(COUNT(T358:U358)=2,ROUND((U358-T358)*1440,0),0)</f>
@@ -31351,7 +31351,7 @@
         <v/>
       </c>
       <c r="R359" s="5" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S359" s="5" t="n">
         <v>0.71875</v>
@@ -31439,16 +31439,16 @@
         <v/>
       </c>
       <c r="R360" s="5" t="n">
-        <v>0.5</v>
+        <v>0.46875</v>
       </c>
       <c r="S360" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="T360" s="5" t="n">
+        <v>0.5520833333333334</v>
+      </c>
+      <c r="U360" s="5" t="n">
         <v>0.59375</v>
-      </c>
-      <c r="U360" s="5" t="n">
-        <v>0.6354166666666666</v>
       </c>
       <c r="V360" s="3">
         <f>IF(COUNT(T360:U360)=2,ROUND((U360-T360)*1440,0),0)</f>
@@ -31679,16 +31679,16 @@
         <v/>
       </c>
       <c r="R363" s="5" t="n">
-        <v>0.4375</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="S363" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.59375</v>
       </c>
       <c r="T363" s="5" t="n">
-        <v>0.53125</v>
+        <v>0.46875</v>
       </c>
       <c r="U363" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="V363" s="3">
         <f>IF(COUNT(T363:U363)=2,ROUND((U363-T363)*1440,0),0)</f>
@@ -31770,13 +31770,13 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="S364" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.59375</v>
       </c>
       <c r="T364" s="5" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="U364" s="5" t="n">
         <v>0.5104166666666666</v>
-      </c>
-      <c r="U364" s="5" t="n">
-        <v>0.5520833333333334</v>
       </c>
       <c r="V364" s="3">
         <f>IF(COUNT(T364:U364)=2,ROUND((U364-T364)*1440,0),0)</f>
@@ -31861,10 +31861,10 @@
         <v>0.6354166666666666</v>
       </c>
       <c r="T365" s="5" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="U365" s="5" t="n">
         <v>0.5104166666666666</v>
-      </c>
-      <c r="U365" s="5" t="n">
-        <v>0.5520833333333334</v>
       </c>
       <c r="V365" s="3">
         <f>IF(COUNT(T365:U365)=2,ROUND((U365-T365)*1440,0),0)</f>
@@ -31946,13 +31946,13 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="S366" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="T366" s="5" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="U366" s="5" t="n">
         <v>0.5104166666666666</v>
-      </c>
-      <c r="U366" s="5" t="n">
-        <v>0.5520833333333334</v>
       </c>
       <c r="V366" s="3">
         <f>IF(COUNT(T366:U366)=2,ROUND((U366-T366)*1440,0),0)</f>
@@ -32118,13 +32118,13 @@
         <v>0.46875</v>
       </c>
       <c r="S368" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="T368" s="5" t="n">
-        <v>0.5625</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="U368" s="5" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="V368" s="3">
         <f>IF(COUNT(T368:U368)=2,ROUND((U368-T368)*1440,0),0)</f>
@@ -32206,13 +32206,13 @@
         <v>0.46875</v>
       </c>
       <c r="S369" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="T369" s="5" t="n">
-        <v>0.5625</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="U369" s="5" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="V369" s="3">
         <f>IF(COUNT(T369:U369)=2,ROUND((U369-T369)*1440,0),0)</f>
@@ -32294,13 +32294,13 @@
         <v>0.4583333333333333</v>
       </c>
       <c r="S370" s="5" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="T370" s="5" t="n">
+        <v>0.5104166666666666</v>
+      </c>
+      <c r="U370" s="5" t="n">
         <v>0.5520833333333334</v>
-      </c>
-      <c r="U370" s="5" t="n">
-        <v>0.59375</v>
       </c>
       <c r="V370" s="3">
         <f>IF(COUNT(T370:U370)=2,ROUND((U370-T370)*1440,0),0)</f>
@@ -32379,16 +32379,16 @@
         <v/>
       </c>
       <c r="R371" s="5" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S371" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="T371" s="5" t="n">
+        <v>0.5520833333333334</v>
+      </c>
+      <c r="U371" s="5" t="n">
         <v>0.59375</v>
-      </c>
-      <c r="U371" s="5" t="n">
-        <v>0.6354166666666666</v>
       </c>
       <c r="V371" s="3">
         <f>IF(COUNT(T371:U371)=2,ROUND((U371-T371)*1440,0),0)</f>
@@ -32467,7 +32467,7 @@
         <v/>
       </c>
       <c r="R372" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="S372" s="5" t="n">
         <v>0.7083333333333334</v>
@@ -32631,16 +32631,16 @@
         <v/>
       </c>
       <c r="R374" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="S374" s="5" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="T374" s="5" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="U374" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.65625</v>
       </c>
       <c r="V374" s="3">
         <f>IF(COUNT(T374:U374)=2,ROUND((U374-T374)*1440,0),0)</f>
@@ -32719,16 +32719,16 @@
         <v/>
       </c>
       <c r="R375" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="S375" s="5" t="n">
-        <v>0.78125</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="T375" s="5" t="n">
+        <v>0.6145833333333334</v>
+      </c>
+      <c r="U375" s="5" t="n">
         <v>0.65625</v>
-      </c>
-      <c r="U375" s="5" t="n">
-        <v>0.6979166666666666</v>
       </c>
       <c r="V375" s="3">
         <f>IF(COUNT(T375:U375)=2,ROUND((U375-T375)*1440,0),0)</f>
@@ -32807,16 +32807,16 @@
         <v/>
       </c>
       <c r="R376" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="S376" s="5" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.75</v>
       </c>
       <c r="T376" s="5" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.625</v>
       </c>
       <c r="U376" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="V376" s="3">
         <f>IF(COUNT(T376:U376)=2,ROUND((U376-T376)*1440,0),0)</f>
@@ -32895,16 +32895,16 @@
         <v/>
       </c>
       <c r="R377" s="5" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.5625</v>
       </c>
       <c r="S377" s="5" t="n">
-        <v>0.78125</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="T377" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="U377" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.71875</v>
       </c>
       <c r="V377" s="3">
         <f>IF(COUNT(T377:U377)=2,ROUND((U377-T377)*1440,0),0)</f>
@@ -32983,16 +32983,16 @@
         <v/>
       </c>
       <c r="R378" s="5" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="S378" s="5" t="n">
-        <v>0.78125</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="T378" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="U378" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.71875</v>
       </c>
       <c r="V378" s="3">
         <f>IF(COUNT(T378:U378)=2,ROUND((U378-T378)*1440,0),0)</f>
@@ -33147,16 +33147,16 @@
         <v/>
       </c>
       <c r="R380" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="S380" s="5" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.71875</v>
       </c>
       <c r="T380" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.59375</v>
       </c>
       <c r="U380" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="V380" s="3">
         <f>IF(COUNT(T380:U380)=2,ROUND((U380-T380)*1440,0),0)</f>
@@ -33235,7 +33235,7 @@
         <v/>
       </c>
       <c r="R381" s="5" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="S381" s="5" t="n">
         <v>0.71875</v>
@@ -33399,16 +33399,16 @@
         <v/>
       </c>
       <c r="R383" s="5" t="n">
-        <v>0.4375</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="S383" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.59375</v>
       </c>
       <c r="T383" s="5" t="n">
-        <v>0.53125</v>
+        <v>0.46875</v>
       </c>
       <c r="U383" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="V383" s="3">
         <f>IF(COUNT(T383:U383)=2,ROUND((U383-T383)*1440,0),0)</f>
@@ -33487,16 +33487,16 @@
         <v/>
       </c>
       <c r="R384" s="5" t="n">
-        <v>0.4375</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="S384" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.59375</v>
       </c>
       <c r="T384" s="5" t="n">
-        <v>0.53125</v>
+        <v>0.46875</v>
       </c>
       <c r="U384" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="V384" s="3">
         <f>IF(COUNT(T384:U384)=2,ROUND((U384-T384)*1440,0),0)</f>
@@ -33575,16 +33575,16 @@
         <v/>
       </c>
       <c r="R385" s="5" t="n">
-        <v>0.4270833333333333</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="S385" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.59375</v>
       </c>
       <c r="T385" s="5" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.46875</v>
       </c>
       <c r="U385" s="5" t="n">
-        <v>0.5625</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="V385" s="3">
         <f>IF(COUNT(T385:U385)=2,ROUND((U385-T385)*1440,0),0)</f>
@@ -33669,10 +33669,10 @@
         <v>0.6354166666666666</v>
       </c>
       <c r="T386" s="5" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="U386" s="5" t="n">
         <v>0.5104166666666666</v>
-      </c>
-      <c r="U386" s="5" t="n">
-        <v>0.5520833333333334</v>
       </c>
       <c r="V386" s="3">
         <f>IF(COUNT(T386:U386)=2,ROUND((U386-T386)*1440,0),0)</f>
@@ -33754,13 +33754,13 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="S387" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="T387" s="5" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="U387" s="5" t="n">
         <v>0.5104166666666666</v>
-      </c>
-      <c r="U387" s="5" t="n">
-        <v>0.5520833333333334</v>
       </c>
       <c r="V387" s="3">
         <f>IF(COUNT(T387:U387)=2,ROUND((U387-T387)*1440,0),0)</f>
@@ -33999,16 +33999,16 @@
         <v/>
       </c>
       <c r="R390" s="5" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S390" s="5" t="n">
-        <v>0.75</v>
+        <v>0.71875</v>
       </c>
       <c r="T390" s="5" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="U390" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.59375</v>
       </c>
       <c r="V390" s="3">
         <f>IF(COUNT(T390:U390)=2,ROUND((U390-T390)*1440,0),0)</f>
@@ -34087,16 +34087,16 @@
         <v/>
       </c>
       <c r="R391" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="S391" s="5" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="T391" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="U391" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.625</v>
       </c>
       <c r="V391" s="3">
         <f>IF(COUNT(T391:U391)=2,ROUND((U391-T391)*1440,0),0)</f>
@@ -34175,7 +34175,7 @@
         <v/>
       </c>
       <c r="R392" s="5" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S392" s="5" t="n">
         <v>0.71875</v>
@@ -34263,16 +34263,16 @@
         <v/>
       </c>
       <c r="R393" s="5" t="n">
-        <v>0.5</v>
+        <v>0.46875</v>
       </c>
       <c r="S393" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="T393" s="5" t="n">
+        <v>0.5520833333333334</v>
+      </c>
+      <c r="U393" s="5" t="n">
         <v>0.59375</v>
-      </c>
-      <c r="U393" s="5" t="n">
-        <v>0.6354166666666666</v>
       </c>
       <c r="V393" s="3">
         <f>IF(COUNT(T393:U393)=2,ROUND((U393-T393)*1440,0),0)</f>
@@ -34427,16 +34427,16 @@
         <v/>
       </c>
       <c r="R395" s="5" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S395" s="5" t="n">
-        <v>0.75</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="T395" s="5" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="U395" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.625</v>
       </c>
       <c r="V395" s="3">
         <f>IF(COUNT(T395:U395)=2,ROUND((U395-T395)*1440,0),0)</f>
@@ -34515,16 +34515,16 @@
         <v/>
       </c>
       <c r="R396" s="5" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S396" s="5" t="n">
-        <v>0.75</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="T396" s="5" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="U396" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.625</v>
       </c>
       <c r="V396" s="3">
         <f>IF(COUNT(T396:U396)=2,ROUND((U396-T396)*1440,0),0)</f>
@@ -34603,16 +34603,16 @@
         <v/>
       </c>
       <c r="R397" s="5" t="n">
-        <v>0.5</v>
+        <v>0.46875</v>
       </c>
       <c r="S397" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="T397" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.5729166666666666</v>
       </c>
       <c r="U397" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="V397" s="3">
         <f>IF(COUNT(T397:U397)=2,ROUND((U397-T397)*1440,0),0)</f>
@@ -34691,16 +34691,16 @@
         <v/>
       </c>
       <c r="R398" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="S398" s="5" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.71875</v>
       </c>
       <c r="T398" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.59375</v>
       </c>
       <c r="U398" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="V398" s="3">
         <f>IF(COUNT(T398:U398)=2,ROUND((U398-T398)*1440,0),0)</f>
@@ -34779,7 +34779,7 @@
         <v/>
       </c>
       <c r="R399" s="5" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="S399" s="5" t="n">
         <v>0.71875</v>
@@ -34943,16 +34943,16 @@
         <v/>
       </c>
       <c r="R401" s="5" t="n">
-        <v>0.5625</v>
+        <v>0.5729166666666666</v>
       </c>
       <c r="S401" s="5" t="n">
-        <v>0.78125</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="T401" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="U401" s="5" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="V401" s="3">
         <f>IF(COUNT(T401:U401)=2,ROUND((U401-T401)*1440,0),0)</f>
@@ -35031,16 +35031,16 @@
         <v/>
       </c>
       <c r="R402" s="5" t="n">
-        <v>0.5625</v>
+        <v>0.5729166666666666</v>
       </c>
       <c r="S402" s="5" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="T402" s="5" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="U402" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="V402" s="3">
         <f>IF(COUNT(T402:U402)=2,ROUND((U402-T402)*1440,0),0)</f>
@@ -35119,16 +35119,16 @@
         <v/>
       </c>
       <c r="R403" s="5" t="n">
-        <v>0.5625</v>
+        <v>0.5729166666666666</v>
       </c>
       <c r="S403" s="5" t="n">
-        <v>0.78125</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="T403" s="5" t="n">
-        <v>0.65625</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="U403" s="5" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="V403" s="3">
         <f>IF(COUNT(T403:U403)=2,ROUND((U403-T403)*1440,0),0)</f>
@@ -35210,13 +35210,13 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="S404" s="5" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="T404" s="5" t="n">
+        <v>0.6354166666666666</v>
+      </c>
+      <c r="U404" s="5" t="n">
         <v>0.6770833333333334</v>
-      </c>
-      <c r="U404" s="5" t="n">
-        <v>0.71875</v>
       </c>
       <c r="V404" s="3">
         <f>IF(COUNT(T404:U404)=2,ROUND((U404-T404)*1440,0),0)</f>
@@ -35298,13 +35298,13 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="S405" s="5" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="T405" s="5" t="n">
+        <v>0.6354166666666666</v>
+      </c>
+      <c r="U405" s="5" t="n">
         <v>0.6770833333333334</v>
-      </c>
-      <c r="U405" s="5" t="n">
-        <v>0.71875</v>
       </c>
       <c r="V405" s="3">
         <f>IF(COUNT(T405:U405)=2,ROUND((U405-T405)*1440,0),0)</f>
@@ -35459,7 +35459,7 @@
         <v/>
       </c>
       <c r="R407" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="S407" s="5" t="n">
         <v>0.6354166666666666</v>
@@ -35547,7 +35547,7 @@
         <v/>
       </c>
       <c r="R408" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="S408" s="5" t="n">
         <v>0.6354166666666666</v>
@@ -35719,16 +35719,16 @@
         <v/>
       </c>
       <c r="R410" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S410" s="5" t="n">
         <v>0.71875</v>
       </c>
       <c r="T410" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.59375</v>
       </c>
       <c r="U410" s="5" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="V410" s="3">
         <f>IF(COUNT(T410:U410)=2,ROUND((U410-T410)*1440,0),0)</f>
@@ -35807,16 +35807,16 @@
         <v/>
       </c>
       <c r="R411" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S411" s="5" t="n">
         <v>0.71875</v>
       </c>
       <c r="T411" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.59375</v>
       </c>
       <c r="U411" s="5" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="V411" s="3">
         <f>IF(COUNT(T411:U411)=2,ROUND((U411-T411)*1440,0),0)</f>
@@ -35895,16 +35895,16 @@
         <v/>
       </c>
       <c r="R412" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S412" s="5" t="n">
-        <v>0.6875</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="T412" s="5" t="n">
-        <v>0.5625</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="U412" s="5" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="V412" s="3">
         <f>IF(COUNT(T412:U412)=2,ROUND((U412-T412)*1440,0),0)</f>
@@ -35983,16 +35983,16 @@
         <v/>
       </c>
       <c r="R413" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="S413" s="5" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="T413" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="U413" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
       <c r="V413" s="3">
         <f>IF(COUNT(T413:U413)=2,ROUND((U413-T413)*1440,0),0)</f>
@@ -36071,16 +36071,16 @@
         <v/>
       </c>
       <c r="R414" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="S414" s="5" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.71875</v>
       </c>
       <c r="T414" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.59375</v>
       </c>
       <c r="U414" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="V414" s="3">
         <f>IF(COUNT(T414:U414)=2,ROUND((U414-T414)*1440,0),0)</f>
@@ -36311,16 +36311,16 @@
         <v/>
       </c>
       <c r="R417" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S417" s="5" t="n">
         <v>0.71875</v>
       </c>
       <c r="T417" s="5" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.59375</v>
       </c>
       <c r="U417" s="5" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="V417" s="3">
         <f>IF(COUNT(T417:U417)=2,ROUND((U417-T417)*1440,0),0)</f>
@@ -36399,16 +36399,16 @@
         <v/>
       </c>
       <c r="R418" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S418" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="T418" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="U418" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="V418" s="3">
         <f>IF(COUNT(T418:U418)=2,ROUND((U418-T418)*1440,0),0)</f>
@@ -36487,16 +36487,16 @@
         <v/>
       </c>
       <c r="R419" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="S419" s="5" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="T419" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="U419" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
       <c r="V419" s="3">
         <f>IF(COUNT(T419:U419)=2,ROUND((U419-T419)*1440,0),0)</f>
@@ -36575,16 +36575,16 @@
         <v/>
       </c>
       <c r="R420" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="S420" s="5" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.71875</v>
       </c>
       <c r="T420" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.59375</v>
       </c>
       <c r="U420" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="V420" s="3">
         <f>IF(COUNT(T420:U420)=2,ROUND((U420-T420)*1440,0),0)</f>
@@ -36739,16 +36739,16 @@
         <v/>
       </c>
       <c r="R422" s="5" t="n">
-        <v>0.4270833333333333</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="S422" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="T422" s="5" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="U422" s="5" t="n">
-        <v>0.5625</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="V422" s="3">
         <f>IF(COUNT(T422:U422)=2,ROUND((U422-T422)*1440,0),0)</f>
@@ -36827,16 +36827,16 @@
         <v/>
       </c>
       <c r="R423" s="5" t="n">
-        <v>0.4270833333333333</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="S423" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="T423" s="5" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="U423" s="5" t="n">
-        <v>0.5625</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="V423" s="3">
         <f>IF(COUNT(T423:U423)=2,ROUND((U423-T423)*1440,0),0)</f>
@@ -36915,16 +36915,16 @@
         <v/>
       </c>
       <c r="R424" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="S424" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="T424" s="5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="U424" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.53125</v>
       </c>
       <c r="V424" s="3">
         <f>IF(COUNT(T424:U424)=2,ROUND((U424-T424)*1440,0),0)</f>
@@ -37003,7 +37003,7 @@
         <v/>
       </c>
       <c r="R425" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="S425" s="5" t="n">
         <v>0.6354166666666666</v>
@@ -37091,7 +37091,7 @@
         <v/>
       </c>
       <c r="R426" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="S426" s="5" t="n">
         <v>0.6354166666666666</v>
@@ -37263,16 +37263,16 @@
         <v/>
       </c>
       <c r="R428" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S428" s="5" t="n">
-        <v>0.75</v>
+        <v>0.71875</v>
       </c>
       <c r="T428" s="5" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="U428" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.59375</v>
       </c>
       <c r="V428" s="3">
         <f>IF(COUNT(T428:U428)=2,ROUND((U428-T428)*1440,0),0)</f>
@@ -37351,16 +37351,16 @@
         <v/>
       </c>
       <c r="R429" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S429" s="5" t="n">
         <v>0.71875</v>
       </c>
       <c r="T429" s="5" t="n">
+        <v>0.5520833333333334</v>
+      </c>
+      <c r="U429" s="5" t="n">
         <v>0.59375</v>
-      </c>
-      <c r="U429" s="5" t="n">
-        <v>0.6354166666666666</v>
       </c>
       <c r="V429" s="3">
         <f>IF(COUNT(T429:U429)=2,ROUND((U429-T429)*1440,0),0)</f>
@@ -37439,16 +37439,16 @@
         <v/>
       </c>
       <c r="R430" s="5" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S430" s="5" t="n">
-        <v>0.71875</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="T430" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="U430" s="5" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="V430" s="3">
         <f>IF(COUNT(T430:U430)=2,ROUND((U430-T430)*1440,0),0)</f>
@@ -37527,16 +37527,16 @@
         <v/>
       </c>
       <c r="R431" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="S431" s="5" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="T431" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="U431" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
       <c r="V431" s="3">
         <f>IF(COUNT(T431:U431)=2,ROUND((U431-T431)*1440,0),0)</f>
@@ -37615,16 +37615,16 @@
         <v/>
       </c>
       <c r="R432" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="S432" s="5" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.71875</v>
       </c>
       <c r="T432" s="5" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.59375</v>
       </c>
       <c r="U432" s="5" t="n">
-        <v>0.59375</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="V432" s="3">
         <f>IF(COUNT(T432:U432)=2,ROUND((U432-T432)*1440,0),0)</f>
@@ -40812,7 +40812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E118"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -40852,1994 +40852,20 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="n">
-        <v>46296</v>
-      </c>
+          <t>Sin alertas</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
       <c r="C2" s="3" t="n"/>
       <c r="D2" s="3" t="n"/>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>10:00: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n">
-        <v>46296</v>
-      </c>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>12:15: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>46296</v>
-      </c>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>12:30: 6 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>46296</v>
-      </c>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>12:45: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>46296</v>
-      </c>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>13:00: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>46296</v>
-      </c>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>13:15: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>46296</v>
-      </c>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>14:00: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>46296</v>
-      </c>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>15:15: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>46297</v>
-      </c>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>10:00: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>46297</v>
-      </c>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>12:15: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>46297</v>
-      </c>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>12:30: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>46297</v>
-      </c>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>12:45: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>46297</v>
-      </c>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>13:00: 6 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>46297</v>
-      </c>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>13:15: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>46297</v>
-      </c>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>14:00: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>46297</v>
-      </c>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>15:15: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>46298</v>
-      </c>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>10:30: 3 en descanso (máximo 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>46298</v>
-      </c>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>10:45: 3 en descanso (máximo 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>46298</v>
-      </c>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>11:00: 3 en descanso (máximo 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>46298</v>
-      </c>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>11:15: 3 en descanso (máximo 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>46302</v>
-      </c>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>12:30: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>46302</v>
-      </c>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>12:45: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>46302</v>
-      </c>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>13:00: 6 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="n">
-        <v>46302</v>
-      </c>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>13:15: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>46302</v>
-      </c>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3" t="n"/>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>13:30: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>46302</v>
-      </c>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>14:15: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>46303</v>
-      </c>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>12:30: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>46303</v>
-      </c>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>12:45: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>46303</v>
-      </c>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="3" t="n"/>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>13:00: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n">
-        <v>46303</v>
-      </c>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="n"/>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>13:15: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="n">
-        <v>46303</v>
-      </c>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="3" t="n"/>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>14:00: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="n">
-        <v>46303</v>
-      </c>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>14:15: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="n">
-        <v>46303</v>
-      </c>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="3" t="n"/>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>14:30: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="n">
-        <v>46304</v>
-      </c>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="n"/>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>12:45: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="n">
-        <v>46304</v>
-      </c>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="n"/>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>13:00: 6 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="n">
-        <v>46304</v>
-      </c>
-      <c r="C37" s="3" t="n"/>
-      <c r="D37" s="3" t="n"/>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>13:15: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="n">
-        <v>46304</v>
-      </c>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="3" t="n"/>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>14:00: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="n">
-        <v>46304</v>
-      </c>
-      <c r="C39" s="3" t="n"/>
-      <c r="D39" s="3" t="n"/>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>14:15: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>46304</v>
-      </c>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="3" t="n"/>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>14:30: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="n">
-        <v>46305</v>
-      </c>
-      <c r="C41" s="3" t="n"/>
-      <c r="D41" s="3" t="n"/>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>10:30: 3 en descanso (máximo 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="n">
-        <v>46305</v>
-      </c>
-      <c r="C42" s="3" t="n"/>
-      <c r="D42" s="3" t="n"/>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>10:45: 3 en descanso (máximo 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="n">
-        <v>46305</v>
-      </c>
-      <c r="C43" s="3" t="n"/>
-      <c r="D43" s="3" t="n"/>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>11:00: 2 en descanso (máximo 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="n">
-        <v>46305</v>
-      </c>
-      <c r="C44" s="3" t="n"/>
-      <c r="D44" s="3" t="n"/>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>11:15: 2 en descanso (máximo 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="n">
-        <v>46309</v>
-      </c>
-      <c r="C45" s="3" t="n"/>
-      <c r="D45" s="3" t="n"/>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>12:30: 6 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="n">
-        <v>46309</v>
-      </c>
-      <c r="C46" s="3" t="n"/>
-      <c r="D46" s="3" t="n"/>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>12:45: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="n">
-        <v>46309</v>
-      </c>
-      <c r="C47" s="3" t="n"/>
-      <c r="D47" s="3" t="n"/>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>13:00: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="n">
-        <v>46309</v>
-      </c>
-      <c r="C48" s="3" t="n"/>
-      <c r="D48" s="3" t="n"/>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>13:15: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="n">
-        <v>46309</v>
-      </c>
-      <c r="C49" s="3" t="n"/>
-      <c r="D49" s="3" t="n"/>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>13:30: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="n">
-        <v>46309</v>
-      </c>
-      <c r="C50" s="3" t="n"/>
-      <c r="D50" s="3" t="n"/>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>14:15: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="C51" s="3" t="n"/>
-      <c r="D51" s="3" t="n"/>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>12:30: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="C52" s="3" t="n"/>
-      <c r="D52" s="3" t="n"/>
-      <c r="E52" s="3" t="inlineStr">
-        <is>
-          <t>12:45: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="C53" s="3" t="n"/>
-      <c r="D53" s="3" t="n"/>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>13:00: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="C54" s="3" t="n"/>
-      <c r="D54" s="3" t="n"/>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>13:15: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="C55" s="3" t="n"/>
-      <c r="D55" s="3" t="n"/>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>14:00: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="C56" s="3" t="n"/>
-      <c r="D56" s="3" t="n"/>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>14:15: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="C57" s="3" t="n"/>
-      <c r="D57" s="3" t="n"/>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>14:30: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="C58" s="3" t="n"/>
-      <c r="D58" s="3" t="n"/>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>12:45: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="C59" s="3" t="n"/>
-      <c r="D59" s="3" t="n"/>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>13:00: 6 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="C60" s="3" t="n"/>
-      <c r="D60" s="3" t="n"/>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>13:15: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="C61" s="3" t="n"/>
-      <c r="D61" s="3" t="n"/>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>14:00: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="C62" s="3" t="n"/>
-      <c r="D62" s="3" t="n"/>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>14:15: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="C63" s="3" t="n"/>
-      <c r="D63" s="3" t="n"/>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>14:30: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="C64" s="3" t="n"/>
-      <c r="D64" s="3" t="n"/>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>10:30: 3 en descanso (máximo 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="C65" s="3" t="n"/>
-      <c r="D65" s="3" t="n"/>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>10:45: 3 en descanso (máximo 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="C66" s="3" t="n"/>
-      <c r="D66" s="3" t="n"/>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>11:00: 2 en descanso (máximo 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="C67" s="3" t="n"/>
-      <c r="D67" s="3" t="n"/>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>11:15: 2 en descanso (máximo 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="n">
-        <v>46314</v>
-      </c>
-      <c r="C68" s="3" t="n"/>
-      <c r="D68" s="3" t="n"/>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>12:45: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="n">
-        <v>46314</v>
-      </c>
-      <c r="C69" s="3" t="n"/>
-      <c r="D69" s="3" t="n"/>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>13:00: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="n">
-        <v>46315</v>
-      </c>
-      <c r="C70" s="3" t="n"/>
-      <c r="D70" s="3" t="n"/>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>12:45: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="n">
-        <v>46315</v>
-      </c>
-      <c r="C71" s="3" t="n"/>
-      <c r="D71" s="3" t="n"/>
-      <c r="E71" s="3" t="inlineStr">
-        <is>
-          <t>13:00: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="n">
-        <v>46316</v>
-      </c>
-      <c r="C72" s="3" t="n"/>
-      <c r="D72" s="3" t="n"/>
-      <c r="E72" s="3" t="inlineStr">
-        <is>
-          <t>12:30: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="n">
-        <v>46316</v>
-      </c>
-      <c r="C73" s="3" t="n"/>
-      <c r="D73" s="3" t="n"/>
-      <c r="E73" s="3" t="inlineStr">
-        <is>
-          <t>12:45: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="n">
-        <v>46316</v>
-      </c>
-      <c r="C74" s="3" t="n"/>
-      <c r="D74" s="3" t="n"/>
-      <c r="E74" s="3" t="inlineStr">
-        <is>
-          <t>13:00: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="n">
-        <v>46316</v>
-      </c>
-      <c r="C75" s="3" t="n"/>
-      <c r="D75" s="3" t="n"/>
-      <c r="E75" s="3" t="inlineStr">
-        <is>
-          <t>13:15: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="n">
-        <v>46316</v>
-      </c>
-      <c r="C76" s="3" t="n"/>
-      <c r="D76" s="3" t="n"/>
-      <c r="E76" s="3" t="inlineStr">
-        <is>
-          <t>13:30: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="n">
-        <v>46316</v>
-      </c>
-      <c r="C77" s="3" t="n"/>
-      <c r="D77" s="3" t="n"/>
-      <c r="E77" s="3" t="inlineStr">
-        <is>
-          <t>14:15: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="n">
-        <v>46316</v>
-      </c>
-      <c r="C78" s="3" t="n"/>
-      <c r="D78" s="3" t="n"/>
-      <c r="E78" s="3" t="inlineStr">
-        <is>
-          <t>14:30: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="n">
-        <v>46317</v>
-      </c>
-      <c r="C79" s="3" t="n"/>
-      <c r="D79" s="3" t="n"/>
-      <c r="E79" s="3" t="inlineStr">
-        <is>
-          <t>10:00: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="n">
-        <v>46317</v>
-      </c>
-      <c r="C80" s="3" t="n"/>
-      <c r="D80" s="3" t="n"/>
-      <c r="E80" s="3" t="inlineStr">
-        <is>
-          <t>12:15: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="n">
-        <v>46317</v>
-      </c>
-      <c r="C81" s="3" t="n"/>
-      <c r="D81" s="3" t="n"/>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>12:30: 6 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="n">
-        <v>46317</v>
-      </c>
-      <c r="C82" s="3" t="n"/>
-      <c r="D82" s="3" t="n"/>
-      <c r="E82" s="3" t="inlineStr">
-        <is>
-          <t>12:45: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="n">
-        <v>46317</v>
-      </c>
-      <c r="C83" s="3" t="n"/>
-      <c r="D83" s="3" t="n"/>
-      <c r="E83" s="3" t="inlineStr">
-        <is>
-          <t>13:00: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="n">
-        <v>46317</v>
-      </c>
-      <c r="C84" s="3" t="n"/>
-      <c r="D84" s="3" t="n"/>
-      <c r="E84" s="3" t="inlineStr">
-        <is>
-          <t>13:15: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B85" s="4" t="n">
-        <v>46317</v>
-      </c>
-      <c r="C85" s="3" t="n"/>
-      <c r="D85" s="3" t="n"/>
-      <c r="E85" s="3" t="inlineStr">
-        <is>
-          <t>14:00: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B86" s="4" t="n">
-        <v>46317</v>
-      </c>
-      <c r="C86" s="3" t="n"/>
-      <c r="D86" s="3" t="n"/>
-      <c r="E86" s="3" t="inlineStr">
-        <is>
-          <t>15:15: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="n">
-        <v>46318</v>
-      </c>
-      <c r="C87" s="3" t="n"/>
-      <c r="D87" s="3" t="n"/>
-      <c r="E87" s="3" t="inlineStr">
-        <is>
-          <t>10:00: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B88" s="4" t="n">
-        <v>46318</v>
-      </c>
-      <c r="C88" s="3" t="n"/>
-      <c r="D88" s="3" t="n"/>
-      <c r="E88" s="3" t="inlineStr">
-        <is>
-          <t>12:15: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="n">
-        <v>46318</v>
-      </c>
-      <c r="C89" s="3" t="n"/>
-      <c r="D89" s="3" t="n"/>
-      <c r="E89" s="3" t="inlineStr">
-        <is>
-          <t>12:30: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="n">
-        <v>46318</v>
-      </c>
-      <c r="C90" s="3" t="n"/>
-      <c r="D90" s="3" t="n"/>
-      <c r="E90" s="3" t="inlineStr">
-        <is>
-          <t>12:45: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="n">
-        <v>46318</v>
-      </c>
-      <c r="C91" s="3" t="n"/>
-      <c r="D91" s="3" t="n"/>
-      <c r="E91" s="3" t="inlineStr">
-        <is>
-          <t>13:00: 6 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="n">
-        <v>46318</v>
-      </c>
-      <c r="C92" s="3" t="n"/>
-      <c r="D92" s="3" t="n"/>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>13:15: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="n">
-        <v>46318</v>
-      </c>
-      <c r="C93" s="3" t="n"/>
-      <c r="D93" s="3" t="n"/>
-      <c r="E93" s="3" t="inlineStr">
-        <is>
-          <t>14:00: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B94" s="4" t="n">
-        <v>46318</v>
-      </c>
-      <c r="C94" s="3" t="n"/>
-      <c r="D94" s="3" t="n"/>
-      <c r="E94" s="3" t="inlineStr">
-        <is>
-          <t>15:15: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="n">
-        <v>46319</v>
-      </c>
-      <c r="C95" s="3" t="n"/>
-      <c r="D95" s="3" t="n"/>
-      <c r="E95" s="3" t="inlineStr">
-        <is>
-          <t>10:30: 3 en descanso (máximo 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="n">
-        <v>46319</v>
-      </c>
-      <c r="C96" s="3" t="n"/>
-      <c r="D96" s="3" t="n"/>
-      <c r="E96" s="3" t="inlineStr">
-        <is>
-          <t>10:45: 3 en descanso (máximo 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="n">
-        <v>46319</v>
-      </c>
-      <c r="C97" s="3" t="n"/>
-      <c r="D97" s="3" t="n"/>
-      <c r="E97" s="3" t="inlineStr">
-        <is>
-          <t>11:00: 3 en descanso (máximo 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="n">
-        <v>46319</v>
-      </c>
-      <c r="C98" s="3" t="n"/>
-      <c r="D98" s="3" t="n"/>
-      <c r="E98" s="3" t="inlineStr">
-        <is>
-          <t>11:15: 3 en descanso (máximo 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="n">
-        <v>46323</v>
-      </c>
-      <c r="C99" s="3" t="n"/>
-      <c r="D99" s="3" t="n"/>
-      <c r="E99" s="3" t="inlineStr">
-        <is>
-          <t>12:30: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B100" s="4" t="n">
-        <v>46323</v>
-      </c>
-      <c r="C100" s="3" t="n"/>
-      <c r="D100" s="3" t="n"/>
-      <c r="E100" s="3" t="inlineStr">
-        <is>
-          <t>12:45: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="n">
-        <v>46323</v>
-      </c>
-      <c r="C101" s="3" t="n"/>
-      <c r="D101" s="3" t="n"/>
-      <c r="E101" s="3" t="inlineStr">
-        <is>
-          <t>13:00: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B102" s="4" t="n">
-        <v>46323</v>
-      </c>
-      <c r="C102" s="3" t="n"/>
-      <c r="D102" s="3" t="n"/>
-      <c r="E102" s="3" t="inlineStr">
-        <is>
-          <t>13:15: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B103" s="4" t="n">
-        <v>46323</v>
-      </c>
-      <c r="C103" s="3" t="n"/>
-      <c r="D103" s="3" t="n"/>
-      <c r="E103" s="3" t="inlineStr">
-        <is>
-          <t>13:30: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B104" s="4" t="n">
-        <v>46323</v>
-      </c>
-      <c r="C104" s="3" t="n"/>
-      <c r="D104" s="3" t="n"/>
-      <c r="E104" s="3" t="inlineStr">
-        <is>
-          <t>14:15: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="n">
-        <v>46323</v>
-      </c>
-      <c r="C105" s="3" t="n"/>
-      <c r="D105" s="3" t="n"/>
-      <c r="E105" s="3" t="inlineStr">
-        <is>
-          <t>14:30: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="n">
-        <v>46324</v>
-      </c>
-      <c r="C106" s="3" t="n"/>
-      <c r="D106" s="3" t="n"/>
-      <c r="E106" s="3" t="inlineStr">
-        <is>
-          <t>12:30: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="n">
-        <v>46324</v>
-      </c>
-      <c r="C107" s="3" t="n"/>
-      <c r="D107" s="3" t="n"/>
-      <c r="E107" s="3" t="inlineStr">
-        <is>
-          <t>12:45: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B108" s="4" t="n">
-        <v>46324</v>
-      </c>
-      <c r="C108" s="3" t="n"/>
-      <c r="D108" s="3" t="n"/>
-      <c r="E108" s="3" t="inlineStr">
-        <is>
-          <t>13:00: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="n">
-        <v>46324</v>
-      </c>
-      <c r="C109" s="3" t="n"/>
-      <c r="D109" s="3" t="n"/>
-      <c r="E109" s="3" t="inlineStr">
-        <is>
-          <t>13:15: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B110" s="4" t="n">
-        <v>46324</v>
-      </c>
-      <c r="C110" s="3" t="n"/>
-      <c r="D110" s="3" t="n"/>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>14:00: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="n">
-        <v>46324</v>
-      </c>
-      <c r="C111" s="3" t="n"/>
-      <c r="D111" s="3" t="n"/>
-      <c r="E111" s="3" t="inlineStr">
-        <is>
-          <t>14:15: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B112" s="4" t="n">
-        <v>46324</v>
-      </c>
-      <c r="C112" s="3" t="n"/>
-      <c r="D112" s="3" t="n"/>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>14:30: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B113" s="4" t="n">
-        <v>46325</v>
-      </c>
-      <c r="C113" s="3" t="n"/>
-      <c r="D113" s="3" t="n"/>
-      <c r="E113" s="3" t="inlineStr">
-        <is>
-          <t>12:45: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B114" s="4" t="n">
-        <v>46325</v>
-      </c>
-      <c r="C114" s="3" t="n"/>
-      <c r="D114" s="3" t="n"/>
-      <c r="E114" s="3" t="inlineStr">
-        <is>
-          <t>13:00: 6 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B115" s="4" t="n">
-        <v>46325</v>
-      </c>
-      <c r="C115" s="3" t="n"/>
-      <c r="D115" s="3" t="n"/>
-      <c r="E115" s="3" t="inlineStr">
-        <is>
-          <t>13:15: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B116" s="4" t="n">
-        <v>46325</v>
-      </c>
-      <c r="C116" s="3" t="n"/>
-      <c r="D116" s="3" t="n"/>
-      <c r="E116" s="3" t="inlineStr">
-        <is>
-          <t>14:00: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B117" s="4" t="n">
-        <v>46325</v>
-      </c>
-      <c r="C117" s="3" t="n"/>
-      <c r="D117" s="3" t="n"/>
-      <c r="E117" s="3" t="inlineStr">
-        <is>
-          <t>14:15: 5 en descanso (máximo 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>DEMASIADOS EN DESCANSO A LA VEZ</t>
-        </is>
-      </c>
-      <c r="B118" s="4" t="n">
-        <v>46325</v>
-      </c>
-      <c r="C118" s="3" t="n"/>
-      <c r="D118" s="3" t="n"/>
-      <c r="E118" s="3" t="inlineStr">
-        <is>
-          <t>14:30: 5 en descanso (máximo 4)</t>
+          <t>La planificación cumple todas las reglas.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E118"/>
+  <autoFilter ref="A1:E2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>